--- a/artfynd/A 56557-2025 artfynd.xlsx
+++ b/artfynd/A 56557-2025 artfynd.xlsx
@@ -675,42 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130108125</v>
+        <v>130107316</v>
       </c>
       <c r="B2" t="n">
-        <v>57741</v>
+        <v>97702</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506976</v>
+        <v>507075</v>
       </c>
       <c r="R2" t="n">
-        <v>7032983</v>
+        <v>7033179</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,43 +752,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,38 +782,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130107316</v>
+        <v>130108125</v>
       </c>
       <c r="B3" t="n">
-        <v>97702</v>
+        <v>57741</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -849,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507075</v>
+        <v>506976</v>
       </c>
       <c r="R3" t="n">
-        <v>7033179</v>
+        <v>7032983</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,19 +863,43 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130108117</v>
+        <v>130107360</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,31 +928,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -960,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507057</v>
+        <v>507211</v>
       </c>
       <c r="R4" t="n">
-        <v>7032982</v>
+        <v>7032876</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +995,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,12 +1004,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1027,9 +1023,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1047,7 +1048,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130107360</v>
+        <v>130107371</v>
       </c>
       <c r="B5" t="n">
         <v>79095</v>
@@ -1076,19 +1077,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507211</v>
+        <v>507222</v>
       </c>
       <c r="R5" t="n">
-        <v>7032876</v>
+        <v>7033039</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,7 +1123,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,34 +1132,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1178,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130107371</v>
+        <v>130108117</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,34 +1161,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507222</v>
+        <v>507057</v>
       </c>
       <c r="R6" t="n">
-        <v>7033039</v>
+        <v>7032982</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1253,7 +1233,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,6 +1244,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -2327,10 +2327,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130107366</v>
+        <v>130108127</v>
       </c>
       <c r="B16" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2338,34 +2338,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507149</v>
+        <v>507051</v>
       </c>
       <c r="R16" t="n">
-        <v>7033155</v>
+        <v>7032835</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2400,19 +2403,35 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2429,10 +2448,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130108115</v>
+        <v>130107366</v>
       </c>
       <c r="B17" t="n">
-        <v>83073</v>
+        <v>79095</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,37 +2459,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506966</v>
+        <v>507149</v>
       </c>
       <c r="R17" t="n">
-        <v>7032974</v>
+        <v>7033155</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2505,30 +2521,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2545,10 +2550,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130108126</v>
+        <v>130108115</v>
       </c>
       <c r="B18" t="n">
-        <v>57900</v>
+        <v>83073</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2556,50 +2561,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507059</v>
+        <v>506966</v>
       </c>
       <c r="R18" t="n">
-        <v>7032796</v>
+        <v>7032974</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2640,12 +2632,23 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2663,10 +2666,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130108127</v>
+        <v>130108126</v>
       </c>
       <c r="B19" t="n">
-        <v>80200</v>
+        <v>57900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2674,37 +2677,50 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507051</v>
+        <v>507059</v>
       </c>
       <c r="R19" t="n">
-        <v>7032835</v>
+        <v>7032796</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2745,28 +2761,12 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -5489,42 +5489,38 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130108123</v>
+        <v>130107314</v>
       </c>
       <c r="B43" t="n">
-        <v>57741</v>
+        <v>97702</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5532,10 +5528,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506984</v>
+        <v>507176</v>
       </c>
       <c r="R43" t="n">
-        <v>7032983</v>
+        <v>7032962</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5570,38 +5566,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5619,7 +5596,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130107314</v>
+        <v>130107315</v>
       </c>
       <c r="B44" t="n">
         <v>97702</v>
@@ -5658,10 +5635,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507176</v>
+        <v>507217</v>
       </c>
       <c r="R44" t="n">
-        <v>7032962</v>
+        <v>7033002</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5726,38 +5703,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130107315</v>
+        <v>130108123</v>
       </c>
       <c r="B45" t="n">
-        <v>97702</v>
+        <v>57741</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5765,10 +5746,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>507217</v>
+        <v>506984</v>
       </c>
       <c r="R45" t="n">
-        <v>7033002</v>
+        <v>7032983</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5803,19 +5784,38 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>

--- a/artfynd/A 56557-2025 artfynd.xlsx
+++ b/artfynd/A 56557-2025 artfynd.xlsx
@@ -1934,10 +1934,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130107361</v>
+        <v>130107307</v>
       </c>
       <c r="B13" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1945,37 +1945,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507236</v>
+        <v>507225</v>
       </c>
       <c r="R13" t="n">
-        <v>7032990</v>
+        <v>7033149</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,7 +2021,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2021,7 +2030,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2042,12 +2050,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2065,27 +2073,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130107307</v>
+        <v>130107328</v>
       </c>
       <c r="B14" t="n">
-        <v>57741</v>
+        <v>57845</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2093,12 +2101,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2112,10 +2124,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507225</v>
+        <v>507190</v>
       </c>
       <c r="R14" t="n">
-        <v>7033149</v>
+        <v>7033178</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2152,7 +2164,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2167,26 +2179,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2204,61 +2196,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130107328</v>
+        <v>130107361</v>
       </c>
       <c r="B15" t="n">
-        <v>57845</v>
+        <v>79095</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507190</v>
+        <v>507236</v>
       </c>
       <c r="R15" t="n">
-        <v>7033178</v>
+        <v>7032990</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2295,7 +2274,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2304,12 +2283,33 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130108127</v>
+        <v>130107366</v>
       </c>
       <c r="B16" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2338,37 +2338,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507051</v>
+        <v>507149</v>
       </c>
       <c r="R16" t="n">
-        <v>7032835</v>
+        <v>7033155</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2403,35 +2400,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2448,10 +2429,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130107366</v>
+        <v>130108115</v>
       </c>
       <c r="B17" t="n">
-        <v>79095</v>
+        <v>83073</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2459,34 +2440,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507149</v>
+        <v>506966</v>
       </c>
       <c r="R17" t="n">
-        <v>7033155</v>
+        <v>7032974</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2521,19 +2505,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2550,10 +2545,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130108115</v>
+        <v>130108126</v>
       </c>
       <c r="B18" t="n">
-        <v>83073</v>
+        <v>57900</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2561,37 +2556,50 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506966</v>
+        <v>507059</v>
       </c>
       <c r="R18" t="n">
-        <v>7032974</v>
+        <v>7032796</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2632,23 +2640,12 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2666,10 +2663,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130108126</v>
+        <v>130108127</v>
       </c>
       <c r="B19" t="n">
-        <v>57900</v>
+        <v>80200</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,50 +2674,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507059</v>
+        <v>507051</v>
       </c>
       <c r="R19" t="n">
-        <v>7032796</v>
+        <v>7032835</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2761,12 +2745,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3617,41 +3617,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130107327</v>
+        <v>130107310</v>
       </c>
       <c r="B27" t="n">
-        <v>80236</v>
+        <v>57738</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3659,10 +3656,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507239</v>
+        <v>507084</v>
       </c>
       <c r="R27" t="n">
-        <v>7032943</v>
+        <v>7033149</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3699,7 +3696,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På en gammal lunglavssälg.</t>
+          <t>Rejäla hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3708,7 +3705,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3719,17 +3715,22 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4053,10 +4054,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130107310</v>
+        <v>130108128</v>
       </c>
       <c r="B31" t="n">
-        <v>57738</v>
+        <v>78107</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4064,27 +4065,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>228579</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507084</v>
+        <v>507058</v>
       </c>
       <c r="R31" t="n">
-        <v>7033149</v>
+        <v>7032972</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4130,25 +4130,16 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ31" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4159,14 +4150,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4184,37 +4170,41 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130108128</v>
+        <v>130107327</v>
       </c>
       <c r="B32" t="n">
-        <v>78107</v>
+        <v>80236</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4222,10 +4212,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>507058</v>
+        <v>507239</v>
       </c>
       <c r="R32" t="n">
-        <v>7032972</v>
+        <v>7032943</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4260,6 +4250,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På en gammal lunglavssälg.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4270,19 +4265,24 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4430,45 +4430,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130107358</v>
+        <v>130107318</v>
       </c>
       <c r="B34" t="n">
-        <v>79095</v>
+        <v>97702</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507233</v>
+        <v>507226</v>
       </c>
       <c r="R34" t="n">
-        <v>7032821</v>
+        <v>7033130</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4503,19 +4507,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4532,10 +4537,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130108116</v>
+        <v>130107358</v>
       </c>
       <c r="B35" t="n">
-        <v>83073</v>
+        <v>79095</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4543,37 +4548,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506959</v>
+        <v>507233</v>
       </c>
       <c r="R35" t="n">
-        <v>7032984</v>
+        <v>7032821</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4608,30 +4610,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4648,10 +4639,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130108124</v>
+        <v>130108116</v>
       </c>
       <c r="B36" t="n">
-        <v>57741</v>
+        <v>83073</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4659,31 +4650,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4691,10 +4677,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506973</v>
+        <v>506959</v>
       </c>
       <c r="R36" t="n">
-        <v>7032980</v>
+        <v>7032984</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4729,24 +4715,15 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -4778,38 +4755,42 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130107318</v>
+        <v>130108124</v>
       </c>
       <c r="B37" t="n">
-        <v>97702</v>
+        <v>57741</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4817,10 +4798,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>507226</v>
+        <v>506973</v>
       </c>
       <c r="R37" t="n">
-        <v>7033130</v>
+        <v>7032980</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4855,19 +4836,38 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4885,10 +4885,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130107367</v>
+        <v>130107325</v>
       </c>
       <c r="B38" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4896,34 +4896,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507157</v>
+        <v>507225</v>
       </c>
       <c r="R38" t="n">
-        <v>7033174</v>
+        <v>7033115</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4960,7 +4963,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4969,8 +4972,34 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4987,10 +5016,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130107325</v>
+        <v>130107367</v>
       </c>
       <c r="B39" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4998,37 +5027,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507225</v>
+        <v>507157</v>
       </c>
       <c r="R39" t="n">
-        <v>7033115</v>
+        <v>7033174</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5065,7 +5091,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5074,34 +5100,8 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5248,10 +5248,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130107372</v>
+        <v>130107306</v>
       </c>
       <c r="B41" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5259,34 +5259,46 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507223</v>
+        <v>507221</v>
       </c>
       <c r="R41" t="n">
-        <v>7033198</v>
+        <v>7033159</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5323,7 +5335,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, enstaka färska och rejält med äldre, påtagligt och tydligt på en granstam.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5334,6 +5346,31 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5350,10 +5387,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130107306</v>
+        <v>130107372</v>
       </c>
       <c r="B42" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5361,46 +5398,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507221</v>
+        <v>507223</v>
       </c>
       <c r="R42" t="n">
-        <v>7033159</v>
+        <v>7033198</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5437,7 +5462,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, enstaka färska och rejält med äldre, påtagligt och tydligt på en granstam.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5448,31 +5473,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">

--- a/artfynd/A 56557-2025 artfynd.xlsx
+++ b/artfynd/A 56557-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130107316</v>
       </c>
       <c r="B2" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130107307</v>
+        <v>130107361</v>
       </c>
       <c r="B13" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1945,46 +1945,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507225</v>
+        <v>507236</v>
       </c>
       <c r="R13" t="n">
-        <v>7033149</v>
+        <v>7032990</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,7 +2012,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2030,6 +2021,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2050,12 +2042,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2073,27 +2065,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130107328</v>
+        <v>130107307</v>
       </c>
       <c r="B14" t="n">
-        <v>57845</v>
+        <v>57741</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2101,16 +2093,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2124,10 +2112,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507190</v>
+        <v>507225</v>
       </c>
       <c r="R14" t="n">
-        <v>7033178</v>
+        <v>7033149</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2164,7 +2152,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
+          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2179,6 +2167,26 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2196,48 +2204,61 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130107361</v>
+        <v>130107328</v>
       </c>
       <c r="B15" t="n">
-        <v>79095</v>
+        <v>57845</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507236</v>
+        <v>507190</v>
       </c>
       <c r="R15" t="n">
-        <v>7032990</v>
+        <v>7033178</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2274,7 +2295,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2283,33 +2304,12 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2545,10 +2545,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130108126</v>
+        <v>130108127</v>
       </c>
       <c r="B18" t="n">
-        <v>57900</v>
+        <v>80200</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2556,50 +2556,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507059</v>
+        <v>507051</v>
       </c>
       <c r="R18" t="n">
-        <v>7032796</v>
+        <v>7032835</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2640,12 +2627,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2663,10 +2666,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130108127</v>
+        <v>130108126</v>
       </c>
       <c r="B19" t="n">
-        <v>80200</v>
+        <v>57900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2674,37 +2677,50 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507051</v>
+        <v>507059</v>
       </c>
       <c r="R19" t="n">
-        <v>7032835</v>
+        <v>7032796</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2745,28 +2761,12 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3020,7 +3020,7 @@
         <v>130107317</v>
       </c>
       <c r="B22" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>130107329</v>
       </c>
       <c r="B23" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3361,10 +3361,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130108129</v>
+        <v>130107324</v>
       </c>
       <c r="B25" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3372,26 +3372,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3399,10 +3403,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507068</v>
+        <v>507238</v>
       </c>
       <c r="R25" t="n">
-        <v>7032840</v>
+        <v>7032941</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3437,6 +3441,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>I riklig mängd på en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3454,17 +3463,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3482,10 +3496,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130107324</v>
+        <v>130108129</v>
       </c>
       <c r="B26" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3493,30 +3507,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3524,10 +3534,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507238</v>
+        <v>507068</v>
       </c>
       <c r="R26" t="n">
-        <v>7032941</v>
+        <v>7032840</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3562,11 +3572,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>I riklig mängd på en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3584,22 +3589,17 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3617,10 +3617,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130107310</v>
+        <v>130107362</v>
       </c>
       <c r="B27" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3628,38 +3628,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507084</v>
+        <v>507201</v>
       </c>
       <c r="R27" t="n">
-        <v>7033149</v>
+        <v>7032984</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3696,7 +3692,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3707,31 +3703,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3748,45 +3719,52 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130107362</v>
+        <v>130107327</v>
       </c>
       <c r="B28" t="n">
-        <v>79095</v>
+        <v>80236</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507201</v>
+        <v>507239</v>
       </c>
       <c r="R28" t="n">
-        <v>7032984</v>
+        <v>7032943</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3823,7 +3801,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en gammal lunglavssälg.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3832,8 +3810,29 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -4054,10 +4053,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130108128</v>
+        <v>130107310</v>
       </c>
       <c r="B31" t="n">
-        <v>78107</v>
+        <v>57738</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4065,26 +4064,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228579</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507058</v>
+        <v>507084</v>
       </c>
       <c r="R31" t="n">
-        <v>7032972</v>
+        <v>7033149</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4130,16 +4130,25 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ31" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4150,9 +4159,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4170,41 +4184,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130107327</v>
+        <v>130108128</v>
       </c>
       <c r="B32" t="n">
-        <v>80236</v>
+        <v>78107</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>228579</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4212,10 +4222,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>507239</v>
+        <v>507058</v>
       </c>
       <c r="R32" t="n">
-        <v>7032943</v>
+        <v>7032972</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4250,11 +4260,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På en gammal lunglavssälg.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4265,24 +4270,19 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4430,38 +4430,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130107318</v>
+        <v>130108124</v>
       </c>
       <c r="B34" t="n">
-        <v>97702</v>
+        <v>57741</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4469,10 +4473,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507226</v>
+        <v>506973</v>
       </c>
       <c r="R34" t="n">
-        <v>7033130</v>
+        <v>7032980</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4507,19 +4511,38 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4537,45 +4560,49 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130107358</v>
+        <v>130107318</v>
       </c>
       <c r="B35" t="n">
-        <v>79095</v>
+        <v>97704</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>507233</v>
+        <v>507226</v>
       </c>
       <c r="R35" t="n">
-        <v>7032821</v>
+        <v>7033130</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4610,19 +4637,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4639,10 +4667,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130108116</v>
+        <v>130107358</v>
       </c>
       <c r="B36" t="n">
-        <v>83073</v>
+        <v>79095</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4650,37 +4678,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506959</v>
+        <v>507233</v>
       </c>
       <c r="R36" t="n">
-        <v>7032984</v>
+        <v>7032821</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4715,30 +4740,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4755,10 +4769,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130108124</v>
+        <v>130108116</v>
       </c>
       <c r="B37" t="n">
-        <v>57741</v>
+        <v>83073</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4766,31 +4780,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4798,10 +4807,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506973</v>
+        <v>506959</v>
       </c>
       <c r="R37" t="n">
-        <v>7032980</v>
+        <v>7032984</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4836,24 +4845,15 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -4885,10 +4885,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130107325</v>
+        <v>130108118</v>
       </c>
       <c r="B38" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4896,26 +4896,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4923,10 +4928,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507225</v>
+        <v>506992</v>
       </c>
       <c r="R38" t="n">
-        <v>7033115</v>
+        <v>7032926</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4963,7 +4968,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4972,33 +4977,27 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5118,10 +5117,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130108118</v>
+        <v>130107325</v>
       </c>
       <c r="B40" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5129,31 +5128,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5161,10 +5155,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506992</v>
+        <v>507225</v>
       </c>
       <c r="R40" t="n">
-        <v>7032926</v>
+        <v>7033115</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5201,7 +5195,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5210,27 +5204,33 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5489,38 +5489,42 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130107314</v>
+        <v>130108123</v>
       </c>
       <c r="B43" t="n">
-        <v>97702</v>
+        <v>57741</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5528,10 +5532,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507176</v>
+        <v>506984</v>
       </c>
       <c r="R43" t="n">
-        <v>7032962</v>
+        <v>7032983</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5566,19 +5570,38 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5596,10 +5619,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130107315</v>
+        <v>130107314</v>
       </c>
       <c r="B44" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5635,10 +5658,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507217</v>
+        <v>507176</v>
       </c>
       <c r="R44" t="n">
-        <v>7033002</v>
+        <v>7032962</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5703,42 +5726,38 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130108123</v>
+        <v>130107315</v>
       </c>
       <c r="B45" t="n">
-        <v>57741</v>
+        <v>97704</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5746,10 +5765,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506984</v>
+        <v>507217</v>
       </c>
       <c r="R45" t="n">
-        <v>7032983</v>
+        <v>7033002</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5784,38 +5803,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5836,7 +5836,7 @@
         <v>130107331</v>
       </c>
       <c r="B46" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>130107319</v>
       </c>
       <c r="B53" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 56557-2025 artfynd.xlsx
+++ b/artfynd/A 56557-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130107316</v>
       </c>
       <c r="B2" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130108125</v>
       </c>
       <c r="B3" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130107360</v>
+        <v>130108117</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,26 +928,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507211</v>
+        <v>507057</v>
       </c>
       <c r="R4" t="n">
-        <v>7032876</v>
+        <v>7032982</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +1000,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,13 +1009,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1023,14 +1027,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1048,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130107371</v>
+        <v>130107360</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1077,16 +1076,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507222</v>
+        <v>507211</v>
       </c>
       <c r="R5" t="n">
-        <v>7033039</v>
+        <v>7032876</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,7 +1125,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,8 +1134,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1150,10 +1178,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130108117</v>
+        <v>130107371</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,42 +1189,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507057</v>
+        <v>507222</v>
       </c>
       <c r="R6" t="n">
-        <v>7032982</v>
+        <v>7033039</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1253,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,26 +1264,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1283,7 +1283,7 @@
         <v>130107373</v>
       </c>
       <c r="B7" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>130108119</v>
       </c>
       <c r="B8" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1512,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130107369</v>
+        <v>130107363</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507237</v>
+        <v>507069</v>
       </c>
       <c r="R9" t="n">
-        <v>7033036</v>
+        <v>7033199</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1614,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130107363</v>
+        <v>130107369</v>
       </c>
       <c r="B10" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507069</v>
+        <v>507237</v>
       </c>
       <c r="R10" t="n">
-        <v>7033199</v>
+        <v>7033036</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1719,7 +1719,7 @@
         <v>130108131</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>130107374</v>
       </c>
       <c r="B12" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>130107361</v>
       </c>
       <c r="B13" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2065,27 +2065,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130107307</v>
+        <v>130107328</v>
       </c>
       <c r="B14" t="n">
-        <v>57741</v>
+        <v>57930</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2093,12 +2093,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2112,10 +2116,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507225</v>
+        <v>507190</v>
       </c>
       <c r="R14" t="n">
-        <v>7033149</v>
+        <v>7033178</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2152,7 +2156,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2167,26 +2171,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2204,27 +2188,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130107328</v>
+        <v>130107307</v>
       </c>
       <c r="B15" t="n">
-        <v>57845</v>
+        <v>57826</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2232,16 +2216,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2255,10 +2235,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507190</v>
+        <v>507225</v>
       </c>
       <c r="R15" t="n">
-        <v>7033178</v>
+        <v>7033149</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2295,7 +2275,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
+          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2310,6 +2290,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2330,7 +2330,7 @@
         <v>130107366</v>
       </c>
       <c r="B16" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>130108115</v>
       </c>
       <c r="B17" t="n">
-        <v>83073</v>
+        <v>83158</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2545,10 +2545,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130108127</v>
+        <v>130108126</v>
       </c>
       <c r="B18" t="n">
-        <v>80200</v>
+        <v>57985</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2556,37 +2556,50 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507051</v>
+        <v>507059</v>
       </c>
       <c r="R18" t="n">
-        <v>7032835</v>
+        <v>7032796</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2627,28 +2640,12 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2666,10 +2663,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130108126</v>
+        <v>130108127</v>
       </c>
       <c r="B19" t="n">
-        <v>57900</v>
+        <v>80285</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,50 +2674,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507059</v>
+        <v>507051</v>
       </c>
       <c r="R19" t="n">
-        <v>7032796</v>
+        <v>7032835</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2761,12 +2745,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2787,7 +2787,7 @@
         <v>130107332</v>
       </c>
       <c r="B20" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2886,37 +2886,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130107370</v>
+        <v>130107317</v>
       </c>
       <c r="B21" t="n">
-        <v>79095</v>
+        <v>97791</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2924,10 +2925,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507211</v>
+        <v>507267</v>
       </c>
       <c r="R21" t="n">
-        <v>7033009</v>
+        <v>7033117</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2962,11 +2963,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligt på flera granar.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2980,26 +2976,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3017,38 +2993,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130107317</v>
+        <v>130107370</v>
       </c>
       <c r="B22" t="n">
-        <v>97704</v>
+        <v>79180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3056,10 +3031,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507267</v>
+        <v>507211</v>
       </c>
       <c r="R22" t="n">
-        <v>7033117</v>
+        <v>7033009</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3094,6 +3069,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3107,6 +3087,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3127,7 +3127,7 @@
         <v>130107329</v>
       </c>
       <c r="B23" t="n">
-        <v>91637</v>
+        <v>91724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>130107364</v>
       </c>
       <c r="B24" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>130107324</v>
       </c>
       <c r="B25" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>130108129</v>
       </c>
       <c r="B26" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3617,10 +3617,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130107362</v>
+        <v>130107365</v>
       </c>
       <c r="B27" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3652,10 +3652,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507201</v>
+        <v>507106</v>
       </c>
       <c r="R27" t="n">
-        <v>7032984</v>
+        <v>7033205</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3692,7 +3692,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3719,52 +3719,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130107327</v>
+        <v>130107368</v>
       </c>
       <c r="B28" t="n">
-        <v>80236</v>
+        <v>79180</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507239</v>
+        <v>507204</v>
       </c>
       <c r="R28" t="n">
-        <v>7032943</v>
+        <v>7033154</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3801,7 +3794,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På en gammal lunglavssälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3810,29 +3803,8 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3849,10 +3821,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130107365</v>
+        <v>130108128</v>
       </c>
       <c r="B29" t="n">
-        <v>79095</v>
+        <v>78192</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3860,34 +3832,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>507106</v>
+        <v>507058</v>
       </c>
       <c r="R29" t="n">
-        <v>7033205</v>
+        <v>7032972</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3922,19 +3897,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3951,10 +3937,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130107368</v>
+        <v>130107362</v>
       </c>
       <c r="B30" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3986,10 +3972,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>507204</v>
+        <v>507201</v>
       </c>
       <c r="R30" t="n">
-        <v>7033154</v>
+        <v>7032984</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4053,38 +4039,41 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130107310</v>
+        <v>130107327</v>
       </c>
       <c r="B31" t="n">
-        <v>57738</v>
+        <v>80321</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4092,10 +4081,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507084</v>
+        <v>507239</v>
       </c>
       <c r="R31" t="n">
-        <v>7033149</v>
+        <v>7032943</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4132,7 +4121,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en gran.</t>
+          <t>På en gammal lunglavssälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4141,6 +4130,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4151,22 +4141,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4184,10 +4169,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130108128</v>
+        <v>130107310</v>
       </c>
       <c r="B32" t="n">
-        <v>78107</v>
+        <v>57823</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4195,26 +4180,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228579</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4222,10 +4208,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>507058</v>
+        <v>507084</v>
       </c>
       <c r="R32" t="n">
-        <v>7032972</v>
+        <v>7033149</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4260,16 +4246,25 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ32" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4280,9 +4275,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4303,7 +4303,7 @@
         <v>130108120</v>
       </c>
       <c r="B33" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4430,10 +4430,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130108124</v>
+        <v>130107358</v>
       </c>
       <c r="B34" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4441,42 +4441,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506973</v>
+        <v>507233</v>
       </c>
       <c r="R34" t="n">
-        <v>7032980</v>
+        <v>7032821</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4513,7 +4505,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4524,26 +4516,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4560,38 +4532,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130107318</v>
+        <v>130108124</v>
       </c>
       <c r="B35" t="n">
-        <v>97704</v>
+        <v>57826</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4599,10 +4575,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>507226</v>
+        <v>506973</v>
       </c>
       <c r="R35" t="n">
-        <v>7033130</v>
+        <v>7032980</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4637,19 +4613,38 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4667,45 +4662,49 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130107358</v>
+        <v>130107318</v>
       </c>
       <c r="B36" t="n">
-        <v>79095</v>
+        <v>97791</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>507233</v>
+        <v>507226</v>
       </c>
       <c r="R36" t="n">
-        <v>7032821</v>
+        <v>7033130</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4740,19 +4739,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4772,7 +4772,7 @@
         <v>130108116</v>
       </c>
       <c r="B37" t="n">
-        <v>83073</v>
+        <v>83158</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>130108118</v>
       </c>
       <c r="B38" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>130107367</v>
       </c>
       <c r="B39" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>130107325</v>
       </c>
       <c r="B40" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5248,10 +5248,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130107306</v>
+        <v>130107372</v>
       </c>
       <c r="B41" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5259,46 +5259,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507221</v>
+        <v>507223</v>
       </c>
       <c r="R41" t="n">
-        <v>7033159</v>
+        <v>7033198</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5335,7 +5323,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, enstaka färska och rejält med äldre, påtagligt och tydligt på en granstam.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5346,31 +5334,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5387,10 +5350,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130107372</v>
+        <v>130107306</v>
       </c>
       <c r="B42" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5398,34 +5361,46 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507223</v>
+        <v>507221</v>
       </c>
       <c r="R42" t="n">
-        <v>7033198</v>
+        <v>7033159</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5462,7 +5437,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, enstaka färska och rejält med äldre, påtagligt och tydligt på en granstam.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5473,6 +5448,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5492,7 +5492,7 @@
         <v>130108123</v>
       </c>
       <c r="B43" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
         <v>130107314</v>
       </c>
       <c r="B44" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>130107315</v>
       </c>
       <c r="B45" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>130107331</v>
       </c>
       <c r="B46" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>130107359</v>
       </c>
       <c r="B47" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6066,10 +6066,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130108130</v>
+        <v>130108121</v>
       </c>
       <c r="B48" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6077,26 +6077,31 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6104,10 +6109,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506954</v>
+        <v>506981</v>
       </c>
       <c r="R48" t="n">
-        <v>7033030</v>
+        <v>7032960</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6142,15 +6147,24 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
@@ -6182,10 +6196,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130108121</v>
+        <v>130108130</v>
       </c>
       <c r="B49" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6193,31 +6207,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6225,10 +6234,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506981</v>
+        <v>506954</v>
       </c>
       <c r="R49" t="n">
-        <v>7032960</v>
+        <v>7033030</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6263,24 +6272,15 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -6312,41 +6312,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130107309</v>
+        <v>130108114</v>
       </c>
       <c r="B50" t="n">
-        <v>80229</v>
+        <v>83158</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6354,10 +6350,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507227</v>
+        <v>507064</v>
       </c>
       <c r="R50" t="n">
-        <v>7032981</v>
+        <v>7032974</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6392,11 +6388,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På en sälg i granskog.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6407,29 +6398,19 @@
       <c r="AG50" t="b">
         <v>0</v>
       </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6447,37 +6428,38 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130108114</v>
+        <v>130107319</v>
       </c>
       <c r="B51" t="n">
-        <v>83073</v>
+        <v>97791</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6485,10 +6467,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507064</v>
+        <v>507144</v>
       </c>
       <c r="R51" t="n">
-        <v>7032974</v>
+        <v>7033068</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6533,19 +6515,9 @@
       <c r="AG51" t="b">
         <v>0</v>
       </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6566,7 +6538,7 @@
         <v>130108122</v>
       </c>
       <c r="B52" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6693,10 +6665,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130107319</v>
+        <v>130107309</v>
       </c>
       <c r="B53" t="n">
-        <v>97704</v>
+        <v>80314</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6704,27 +6676,30 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6732,10 +6707,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>507144</v>
+        <v>507227</v>
       </c>
       <c r="R53" t="n">
-        <v>7033068</v>
+        <v>7032981</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6770,6 +6745,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På en sälg i granskog.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6783,6 +6763,26 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>

--- a/artfynd/A 56557-2025 artfynd.xlsx
+++ b/artfynd/A 56557-2025 artfynd.xlsx
@@ -1512,7 +1512,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130107363</v>
+        <v>130108131</v>
       </c>
       <c r="B9" t="n">
         <v>79180</v>
@@ -1541,16 +1541,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507069</v>
+        <v>506958</v>
       </c>
       <c r="R9" t="n">
-        <v>7033199</v>
+        <v>7032984</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1585,19 +1588,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1716,7 +1730,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130108131</v>
+        <v>130107363</v>
       </c>
       <c r="B11" t="n">
         <v>79180</v>
@@ -1745,19 +1759,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506958</v>
+        <v>507069</v>
       </c>
       <c r="R11" t="n">
-        <v>7032984</v>
+        <v>7033199</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,30 +1803,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1934,10 +1934,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130107361</v>
+        <v>130107307</v>
       </c>
       <c r="B13" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1945,37 +1945,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507236</v>
+        <v>507225</v>
       </c>
       <c r="R13" t="n">
-        <v>7032990</v>
+        <v>7033149</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,7 +2021,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2021,7 +2030,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2042,12 +2050,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2065,61 +2073,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130107328</v>
+        <v>130107361</v>
       </c>
       <c r="B14" t="n">
-        <v>57930</v>
+        <v>79180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507190</v>
+        <v>507236</v>
       </c>
       <c r="R14" t="n">
-        <v>7033178</v>
+        <v>7032990</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2156,7 +2151,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,12 +2160,33 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2188,27 +2204,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130107307</v>
+        <v>130107328</v>
       </c>
       <c r="B15" t="n">
-        <v>57826</v>
+        <v>57930</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2216,12 +2232,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2235,10 +2255,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507225</v>
+        <v>507190</v>
       </c>
       <c r="R15" t="n">
-        <v>7033149</v>
+        <v>7033178</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2275,7 +2295,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2290,26 +2310,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -3361,10 +3361,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130107324</v>
+        <v>130108129</v>
       </c>
       <c r="B25" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3372,30 +3372,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3403,10 +3399,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507238</v>
+        <v>507068</v>
       </c>
       <c r="R25" t="n">
-        <v>7032941</v>
+        <v>7032840</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3441,11 +3437,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>I riklig mängd på en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3463,22 +3454,17 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3496,10 +3482,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130108129</v>
+        <v>130107324</v>
       </c>
       <c r="B26" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3507,26 +3493,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3534,10 +3524,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507068</v>
+        <v>507238</v>
       </c>
       <c r="R26" t="n">
-        <v>7032840</v>
+        <v>7032941</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3572,6 +3562,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>I riklig mängd på en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3589,17 +3584,22 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3617,10 +3617,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130107365</v>
+        <v>130108128</v>
       </c>
       <c r="B27" t="n">
-        <v>79180</v>
+        <v>78192</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3628,34 +3628,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507106</v>
+        <v>507058</v>
       </c>
       <c r="R27" t="n">
-        <v>7033205</v>
+        <v>7032972</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3690,19 +3693,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3719,7 +3733,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130107368</v>
+        <v>130107362</v>
       </c>
       <c r="B28" t="n">
         <v>79180</v>
@@ -3754,10 +3768,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507204</v>
+        <v>507201</v>
       </c>
       <c r="R28" t="n">
-        <v>7033154</v>
+        <v>7032984</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3821,37 +3835,41 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130108128</v>
+        <v>130107327</v>
       </c>
       <c r="B29" t="n">
-        <v>78192</v>
+        <v>80321</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3859,10 +3877,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>507058</v>
+        <v>507239</v>
       </c>
       <c r="R29" t="n">
-        <v>7032972</v>
+        <v>7032943</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3897,6 +3915,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På en gammal lunglavssälg.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3907,19 +3930,24 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3937,7 +3965,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130107362</v>
+        <v>130107365</v>
       </c>
       <c r="B30" t="n">
         <v>79180</v>
@@ -3972,10 +4000,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>507201</v>
+        <v>507106</v>
       </c>
       <c r="R30" t="n">
-        <v>7032984</v>
+        <v>7033205</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4012,7 +4040,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4039,52 +4067,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130107327</v>
+        <v>130107368</v>
       </c>
       <c r="B31" t="n">
-        <v>80321</v>
+        <v>79180</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507239</v>
+        <v>507204</v>
       </c>
       <c r="R31" t="n">
-        <v>7032943</v>
+        <v>7033154</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4121,7 +4142,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På en gammal lunglavssälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4130,29 +4151,8 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">

--- a/artfynd/A 56557-2025 artfynd.xlsx
+++ b/artfynd/A 56557-2025 artfynd.xlsx
@@ -1512,7 +1512,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130108131</v>
+        <v>130107363</v>
       </c>
       <c r="B9" t="n">
         <v>79180</v>
@@ -1541,19 +1541,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506958</v>
+        <v>507069</v>
       </c>
       <c r="R9" t="n">
-        <v>7032984</v>
+        <v>7033199</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1588,30 +1585,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1730,7 +1716,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130107363</v>
+        <v>130108131</v>
       </c>
       <c r="B11" t="n">
         <v>79180</v>
@@ -1759,16 +1745,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507069</v>
+        <v>506958</v>
       </c>
       <c r="R11" t="n">
-        <v>7033199</v>
+        <v>7032984</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1803,19 +1792,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1934,10 +1934,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130107307</v>
+        <v>130107361</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1945,46 +1945,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507225</v>
+        <v>507236</v>
       </c>
       <c r="R13" t="n">
-        <v>7033149</v>
+        <v>7032990</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,7 +2012,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2030,6 +2021,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2050,12 +2042,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2073,48 +2065,61 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130107361</v>
+        <v>130107328</v>
       </c>
       <c r="B14" t="n">
-        <v>79180</v>
+        <v>57930</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507236</v>
+        <v>507190</v>
       </c>
       <c r="R14" t="n">
-        <v>7032990</v>
+        <v>7033178</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2151,7 +2156,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2160,33 +2165,12 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2204,27 +2188,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130107328</v>
+        <v>130107307</v>
       </c>
       <c r="B15" t="n">
-        <v>57930</v>
+        <v>57826</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2232,16 +2216,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2255,10 +2235,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507190</v>
+        <v>507225</v>
       </c>
       <c r="R15" t="n">
-        <v>7033178</v>
+        <v>7033149</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2295,7 +2275,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
+          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2310,6 +2290,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -3361,10 +3361,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130108129</v>
+        <v>130107324</v>
       </c>
       <c r="B25" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3372,26 +3372,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3399,10 +3403,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507068</v>
+        <v>507238</v>
       </c>
       <c r="R25" t="n">
-        <v>7032840</v>
+        <v>7032941</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3437,6 +3441,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>I riklig mängd på en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3454,17 +3463,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3482,10 +3496,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130107324</v>
+        <v>130108129</v>
       </c>
       <c r="B26" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3493,30 +3507,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3524,10 +3534,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507238</v>
+        <v>507068</v>
       </c>
       <c r="R26" t="n">
-        <v>7032941</v>
+        <v>7032840</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3562,11 +3572,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>I riklig mängd på en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3584,22 +3589,17 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -5489,42 +5489,38 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130108123</v>
+        <v>130107314</v>
       </c>
       <c r="B43" t="n">
-        <v>57826</v>
+        <v>97791</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5532,10 +5528,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506984</v>
+        <v>507176</v>
       </c>
       <c r="R43" t="n">
-        <v>7032983</v>
+        <v>7032962</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5570,38 +5566,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5619,7 +5596,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130107314</v>
+        <v>130107315</v>
       </c>
       <c r="B44" t="n">
         <v>97791</v>
@@ -5658,10 +5635,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507176</v>
+        <v>507217</v>
       </c>
       <c r="R44" t="n">
-        <v>7032962</v>
+        <v>7033002</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5726,38 +5703,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130107315</v>
+        <v>130108123</v>
       </c>
       <c r="B45" t="n">
-        <v>97791</v>
+        <v>57826</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5765,10 +5746,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>507217</v>
+        <v>506984</v>
       </c>
       <c r="R45" t="n">
-        <v>7033002</v>
+        <v>7032983</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5803,19 +5784,38 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>

--- a/artfynd/A 56557-2025 artfynd.xlsx
+++ b/artfynd/A 56557-2025 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130108117</v>
+        <v>130107360</v>
       </c>
       <c r="B4" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,31 +928,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -960,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507057</v>
+        <v>507211</v>
       </c>
       <c r="R4" t="n">
-        <v>7032982</v>
+        <v>7032876</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +995,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,12 +1004,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1027,9 +1023,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1047,7 +1048,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130107360</v>
+        <v>130107371</v>
       </c>
       <c r="B5" t="n">
         <v>79180</v>
@@ -1076,19 +1077,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507211</v>
+        <v>507222</v>
       </c>
       <c r="R5" t="n">
-        <v>7032876</v>
+        <v>7033039</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,7 +1123,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,34 +1132,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1178,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130107371</v>
+        <v>130108117</v>
       </c>
       <c r="B6" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,34 +1161,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507222</v>
+        <v>507057</v>
       </c>
       <c r="R6" t="n">
-        <v>7033039</v>
+        <v>7032982</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1253,7 +1233,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,6 +1244,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1512,7 +1512,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130107363</v>
+        <v>130107369</v>
       </c>
       <c r="B9" t="n">
         <v>79180</v>
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507069</v>
+        <v>507237</v>
       </c>
       <c r="R9" t="n">
-        <v>7033199</v>
+        <v>7033036</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1614,7 +1614,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130107369</v>
+        <v>130107363</v>
       </c>
       <c r="B10" t="n">
         <v>79180</v>
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507237</v>
+        <v>507069</v>
       </c>
       <c r="R10" t="n">
-        <v>7033036</v>
+        <v>7033199</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1934,48 +1934,61 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130107361</v>
+        <v>130107328</v>
       </c>
       <c r="B13" t="n">
-        <v>79180</v>
+        <v>57930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507236</v>
+        <v>507190</v>
       </c>
       <c r="R13" t="n">
-        <v>7032990</v>
+        <v>7033178</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,7 +2025,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2021,33 +2034,12 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2065,61 +2057,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130107328</v>
+        <v>130107361</v>
       </c>
       <c r="B14" t="n">
-        <v>57930</v>
+        <v>79180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507190</v>
+        <v>507236</v>
       </c>
       <c r="R14" t="n">
-        <v>7033178</v>
+        <v>7032990</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2156,7 +2135,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,12 +2144,33 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2545,10 +2545,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130108126</v>
+        <v>130108127</v>
       </c>
       <c r="B18" t="n">
-        <v>57985</v>
+        <v>80285</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2556,50 +2556,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507059</v>
+        <v>507051</v>
       </c>
       <c r="R18" t="n">
-        <v>7032796</v>
+        <v>7032835</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2640,12 +2627,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2663,10 +2666,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130108127</v>
+        <v>130108126</v>
       </c>
       <c r="B19" t="n">
-        <v>80285</v>
+        <v>57985</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2674,37 +2677,50 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507051</v>
+        <v>507059</v>
       </c>
       <c r="R19" t="n">
-        <v>7032835</v>
+        <v>7032796</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2745,28 +2761,12 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2886,38 +2886,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130107317</v>
+        <v>130107370</v>
       </c>
       <c r="B21" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2925,10 +2924,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507267</v>
+        <v>507211</v>
       </c>
       <c r="R21" t="n">
-        <v>7033117</v>
+        <v>7033009</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2963,6 +2962,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2976,6 +2980,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2993,37 +3017,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130107370</v>
+        <v>130107317</v>
       </c>
       <c r="B22" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3031,10 +3056,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507211</v>
+        <v>507267</v>
       </c>
       <c r="R22" t="n">
-        <v>7033009</v>
+        <v>7033117</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3069,11 +3094,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt på flera granar.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3087,26 +3107,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3617,10 +3617,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130108128</v>
+        <v>130107362</v>
       </c>
       <c r="B27" t="n">
-        <v>78192</v>
+        <v>79180</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3628,37 +3628,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507058</v>
+        <v>507201</v>
       </c>
       <c r="R27" t="n">
-        <v>7032972</v>
+        <v>7032984</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3693,30 +3690,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3733,45 +3719,52 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130107362</v>
+        <v>130107327</v>
       </c>
       <c r="B28" t="n">
-        <v>79180</v>
+        <v>80321</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507201</v>
+        <v>507239</v>
       </c>
       <c r="R28" t="n">
-        <v>7032984</v>
+        <v>7032943</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3808,7 +3801,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en gammal lunglavssälg.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3817,8 +3810,29 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3835,52 +3849,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130107327</v>
+        <v>130107365</v>
       </c>
       <c r="B29" t="n">
-        <v>80321</v>
+        <v>79180</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>507239</v>
+        <v>507106</v>
       </c>
       <c r="R29" t="n">
-        <v>7032943</v>
+        <v>7033205</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3917,7 +3924,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På en gammal lunglavssälg.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3926,29 +3933,8 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3965,7 +3951,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130107365</v>
+        <v>130107368</v>
       </c>
       <c r="B30" t="n">
         <v>79180</v>
@@ -4000,10 +3986,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>507106</v>
+        <v>507204</v>
       </c>
       <c r="R30" t="n">
-        <v>7033205</v>
+        <v>7033154</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4040,7 +4026,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4067,10 +4053,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130107368</v>
+        <v>130107310</v>
       </c>
       <c r="B31" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4078,34 +4064,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507204</v>
+        <v>507084</v>
       </c>
       <c r="R31" t="n">
-        <v>7033154</v>
+        <v>7033149</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4142,7 +4132,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rejäla hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4153,6 +4143,31 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4169,10 +4184,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130107310</v>
+        <v>130108128</v>
       </c>
       <c r="B32" t="n">
-        <v>57823</v>
+        <v>78192</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4180,27 +4195,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>228579</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4208,10 +4222,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>507084</v>
+        <v>507058</v>
       </c>
       <c r="R32" t="n">
-        <v>7033149</v>
+        <v>7032972</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4246,25 +4260,16 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ32" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4275,14 +4280,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4430,45 +4430,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130107358</v>
+        <v>130107318</v>
       </c>
       <c r="B34" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507233</v>
+        <v>507226</v>
       </c>
       <c r="R34" t="n">
-        <v>7032821</v>
+        <v>7033130</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4503,19 +4507,20 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4532,10 +4537,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130108124</v>
+        <v>130107358</v>
       </c>
       <c r="B35" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4543,42 +4548,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506973</v>
+        <v>507233</v>
       </c>
       <c r="R35" t="n">
-        <v>7032980</v>
+        <v>7032821</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4615,7 +4612,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4626,26 +4623,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4662,38 +4639,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130107318</v>
+        <v>130108116</v>
       </c>
       <c r="B36" t="n">
-        <v>97791</v>
+        <v>83158</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4701,10 +4677,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>507226</v>
+        <v>506959</v>
       </c>
       <c r="R36" t="n">
-        <v>7033130</v>
+        <v>7032984</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4749,9 +4725,19 @@
       <c r="AG36" t="b">
         <v>0</v>
       </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4769,10 +4755,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130108116</v>
+        <v>130108124</v>
       </c>
       <c r="B37" t="n">
-        <v>83158</v>
+        <v>57826</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4780,26 +4766,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4807,10 +4798,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506959</v>
+        <v>506973</v>
       </c>
       <c r="R37" t="n">
-        <v>7032984</v>
+        <v>7032980</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4845,15 +4836,24 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -4885,10 +4885,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130108118</v>
+        <v>130107367</v>
       </c>
       <c r="B38" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4896,42 +4896,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506992</v>
+        <v>507157</v>
       </c>
       <c r="R38" t="n">
-        <v>7032926</v>
+        <v>7033174</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4968,7 +4960,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4979,26 +4971,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5015,10 +4987,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130107367</v>
+        <v>130107325</v>
       </c>
       <c r="B39" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5026,34 +4998,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507157</v>
+        <v>507225</v>
       </c>
       <c r="R39" t="n">
-        <v>7033174</v>
+        <v>7033115</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5090,7 +5065,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5099,8 +5074,34 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5117,10 +5118,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130107325</v>
+        <v>130108118</v>
       </c>
       <c r="B40" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5128,26 +5129,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5155,10 +5161,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507225</v>
+        <v>506992</v>
       </c>
       <c r="R40" t="n">
-        <v>7033115</v>
+        <v>7032926</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5195,7 +5201,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5204,33 +5210,27 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6066,10 +6066,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130108121</v>
+        <v>130108130</v>
       </c>
       <c r="B48" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6077,31 +6077,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6109,10 +6104,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506981</v>
+        <v>506954</v>
       </c>
       <c r="R48" t="n">
-        <v>7032960</v>
+        <v>7033030</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6147,24 +6142,15 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
@@ -6196,10 +6182,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130108130</v>
+        <v>130108121</v>
       </c>
       <c r="B49" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6207,26 +6193,31 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6234,10 +6225,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506954</v>
+        <v>506981</v>
       </c>
       <c r="R49" t="n">
-        <v>7033030</v>
+        <v>7032960</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6272,15 +6263,24 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -6312,37 +6312,38 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130108114</v>
+        <v>130107319</v>
       </c>
       <c r="B50" t="n">
-        <v>83158</v>
+        <v>97791</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6350,10 +6351,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507064</v>
+        <v>507144</v>
       </c>
       <c r="R50" t="n">
-        <v>7032974</v>
+        <v>7033068</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6398,19 +6399,9 @@
       <c r="AG50" t="b">
         <v>0</v>
       </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6428,10 +6419,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130107319</v>
+        <v>130107309</v>
       </c>
       <c r="B51" t="n">
-        <v>97791</v>
+        <v>80314</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6439,27 +6430,30 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6467,10 +6461,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507144</v>
+        <v>507227</v>
       </c>
       <c r="R51" t="n">
-        <v>7033068</v>
+        <v>7032981</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6505,6 +6499,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På en sälg i granskog.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6518,6 +6517,26 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6535,10 +6554,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130108122</v>
+        <v>130108114</v>
       </c>
       <c r="B52" t="n">
-        <v>57826</v>
+        <v>83158</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6546,31 +6565,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6578,10 +6592,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506980</v>
+        <v>507064</v>
       </c>
       <c r="R52" t="n">
-        <v>7032966</v>
+        <v>7032974</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6616,24 +6630,15 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
@@ -6665,39 +6670,40 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130107309</v>
+        <v>130108122</v>
       </c>
       <c r="B53" t="n">
-        <v>80314</v>
+        <v>57826</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -6707,10 +6713,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>507227</v>
+        <v>506980</v>
       </c>
       <c r="R53" t="n">
-        <v>7032981</v>
+        <v>7032966</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6747,7 +6753,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På en sälg i granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6756,33 +6762,27 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>

--- a/artfynd/A 56557-2025 artfynd.xlsx
+++ b/artfynd/A 56557-2025 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130107360</v>
+        <v>130108117</v>
       </c>
       <c r="B4" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,26 +928,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507211</v>
+        <v>507057</v>
       </c>
       <c r="R4" t="n">
-        <v>7032876</v>
+        <v>7032982</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +1000,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,13 +1009,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1023,14 +1027,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1150,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130108117</v>
+        <v>130107360</v>
       </c>
       <c r="B6" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,31 +1160,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1193,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507057</v>
+        <v>507211</v>
       </c>
       <c r="R6" t="n">
-        <v>7032982</v>
+        <v>7032876</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1227,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,12 +1236,13 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1260,9 +1255,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1512,7 +1512,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130107369</v>
+        <v>130107363</v>
       </c>
       <c r="B9" t="n">
         <v>79180</v>
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507237</v>
+        <v>507069</v>
       </c>
       <c r="R9" t="n">
-        <v>7033036</v>
+        <v>7033199</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1614,7 +1614,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130107363</v>
+        <v>130108131</v>
       </c>
       <c r="B10" t="n">
         <v>79180</v>
@@ -1643,16 +1643,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507069</v>
+        <v>506958</v>
       </c>
       <c r="R10" t="n">
-        <v>7033199</v>
+        <v>7032984</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,19 +1690,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1716,7 +1730,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130108131</v>
+        <v>130107369</v>
       </c>
       <c r="B11" t="n">
         <v>79180</v>
@@ -1745,19 +1759,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506958</v>
+        <v>507237</v>
       </c>
       <c r="R11" t="n">
-        <v>7032984</v>
+        <v>7033036</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,30 +1803,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1934,61 +1934,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130107328</v>
+        <v>130107361</v>
       </c>
       <c r="B13" t="n">
-        <v>57930</v>
+        <v>79180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507190</v>
+        <v>507236</v>
       </c>
       <c r="R13" t="n">
-        <v>7033178</v>
+        <v>7032990</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2025,7 +2012,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,12 +2021,33 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2057,10 +2065,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130107361</v>
+        <v>130107307</v>
       </c>
       <c r="B14" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,37 +2076,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507236</v>
+        <v>507225</v>
       </c>
       <c r="R14" t="n">
-        <v>7032990</v>
+        <v>7033149</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2135,7 +2152,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,7 +2161,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2165,12 +2181,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2188,27 +2204,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130107307</v>
+        <v>130107328</v>
       </c>
       <c r="B15" t="n">
-        <v>57826</v>
+        <v>57930</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2216,12 +2232,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2235,10 +2255,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507225</v>
+        <v>507190</v>
       </c>
       <c r="R15" t="n">
-        <v>7033149</v>
+        <v>7033178</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2275,7 +2295,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2290,26 +2310,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130107366</v>
+        <v>130108126</v>
       </c>
       <c r="B16" t="n">
-        <v>79180</v>
+        <v>57985</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2338,34 +2338,50 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507149</v>
+        <v>507059</v>
       </c>
       <c r="R16" t="n">
-        <v>7033155</v>
+        <v>7032796</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2400,11 +2416,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2413,6 +2424,11 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2429,10 +2445,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130108115</v>
+        <v>130107366</v>
       </c>
       <c r="B17" t="n">
-        <v>83158</v>
+        <v>79180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,37 +2456,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506966</v>
+        <v>507149</v>
       </c>
       <c r="R17" t="n">
-        <v>7032974</v>
+        <v>7033155</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2505,30 +2518,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2666,10 +2668,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130108126</v>
+        <v>130108115</v>
       </c>
       <c r="B19" t="n">
-        <v>57985</v>
+        <v>83158</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,50 +2679,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507059</v>
+        <v>506966</v>
       </c>
       <c r="R19" t="n">
-        <v>7032796</v>
+        <v>7032974</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2761,12 +2750,23 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3361,10 +3361,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130107324</v>
+        <v>130108129</v>
       </c>
       <c r="B25" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3372,30 +3372,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3403,10 +3399,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507238</v>
+        <v>507068</v>
       </c>
       <c r="R25" t="n">
-        <v>7032941</v>
+        <v>7032840</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3441,11 +3437,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>I riklig mängd på en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3463,22 +3454,17 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3496,10 +3482,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130108129</v>
+        <v>130107324</v>
       </c>
       <c r="B26" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3507,26 +3493,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3534,10 +3524,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507068</v>
+        <v>507238</v>
       </c>
       <c r="R26" t="n">
-        <v>7032840</v>
+        <v>7032941</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3572,6 +3562,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>I riklig mängd på en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3589,17 +3584,22 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3617,10 +3617,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130107362</v>
+        <v>130108128</v>
       </c>
       <c r="B27" t="n">
-        <v>79180</v>
+        <v>78192</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3628,34 +3628,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507201</v>
+        <v>507058</v>
       </c>
       <c r="R27" t="n">
-        <v>7032984</v>
+        <v>7032972</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3690,19 +3693,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3719,52 +3733,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130107327</v>
+        <v>130107362</v>
       </c>
       <c r="B28" t="n">
-        <v>80321</v>
+        <v>79180</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507239</v>
+        <v>507201</v>
       </c>
       <c r="R28" t="n">
-        <v>7032943</v>
+        <v>7032984</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3801,7 +3808,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På en gammal lunglavssälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3810,29 +3817,8 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3849,10 +3835,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130107365</v>
+        <v>130107310</v>
       </c>
       <c r="B29" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3860,34 +3846,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>507106</v>
+        <v>507084</v>
       </c>
       <c r="R29" t="n">
-        <v>7033205</v>
+        <v>7033149</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3924,7 +3914,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Rejäla hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3935,6 +3925,31 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3951,7 +3966,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130107368</v>
+        <v>130107365</v>
       </c>
       <c r="B30" t="n">
         <v>79180</v>
@@ -3986,10 +4001,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>507204</v>
+        <v>507106</v>
       </c>
       <c r="R30" t="n">
-        <v>7033154</v>
+        <v>7033205</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4026,7 +4041,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4053,10 +4068,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130107310</v>
+        <v>130107368</v>
       </c>
       <c r="B31" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4064,38 +4079,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507084</v>
+        <v>507204</v>
       </c>
       <c r="R31" t="n">
-        <v>7033149</v>
+        <v>7033154</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4132,7 +4143,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4143,31 +4154,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4184,37 +4170,41 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130108128</v>
+        <v>130107327</v>
       </c>
       <c r="B32" t="n">
-        <v>78192</v>
+        <v>80321</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4222,10 +4212,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>507058</v>
+        <v>507239</v>
       </c>
       <c r="R32" t="n">
-        <v>7032972</v>
+        <v>7032943</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4260,6 +4250,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På en gammal lunglavssälg.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4270,19 +4265,24 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4430,49 +4430,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130107318</v>
+        <v>130107358</v>
       </c>
       <c r="B34" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507226</v>
+        <v>507233</v>
       </c>
       <c r="R34" t="n">
-        <v>7033130</v>
+        <v>7032821</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4507,20 +4503,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4537,10 +4532,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130107358</v>
+        <v>130108116</v>
       </c>
       <c r="B35" t="n">
-        <v>79180</v>
+        <v>83158</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4548,34 +4543,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>507233</v>
+        <v>506959</v>
       </c>
       <c r="R35" t="n">
-        <v>7032821</v>
+        <v>7032984</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4610,19 +4608,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4639,10 +4648,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130108116</v>
+        <v>130108124</v>
       </c>
       <c r="B36" t="n">
-        <v>83158</v>
+        <v>57826</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4650,26 +4659,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4677,10 +4691,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506959</v>
+        <v>506973</v>
       </c>
       <c r="R36" t="n">
-        <v>7032984</v>
+        <v>7032980</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4715,15 +4729,24 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -4755,42 +4778,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130108124</v>
+        <v>130107318</v>
       </c>
       <c r="B37" t="n">
-        <v>57826</v>
+        <v>97791</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4798,10 +4817,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506973</v>
+        <v>507226</v>
       </c>
       <c r="R37" t="n">
-        <v>7032980</v>
+        <v>7033130</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4836,38 +4855,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5248,10 +5248,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130107372</v>
+        <v>130107306</v>
       </c>
       <c r="B41" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5259,34 +5259,46 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507223</v>
+        <v>507221</v>
       </c>
       <c r="R41" t="n">
-        <v>7033198</v>
+        <v>7033159</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5323,7 +5335,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, enstaka färska och rejält med äldre, påtagligt och tydligt på en granstam.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5334,6 +5346,31 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5350,10 +5387,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130107306</v>
+        <v>130107372</v>
       </c>
       <c r="B42" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5361,46 +5398,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507221</v>
+        <v>507223</v>
       </c>
       <c r="R42" t="n">
-        <v>7033159</v>
+        <v>7033198</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5437,7 +5462,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, enstaka färska och rejält med äldre, påtagligt och tydligt på en granstam.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5448,31 +5473,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5489,38 +5489,42 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130107314</v>
+        <v>130108123</v>
       </c>
       <c r="B43" t="n">
-        <v>97791</v>
+        <v>57826</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5528,10 +5532,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>507176</v>
+        <v>506984</v>
       </c>
       <c r="R43" t="n">
-        <v>7032962</v>
+        <v>7032983</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5566,19 +5570,38 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5703,42 +5726,38 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130108123</v>
+        <v>130107314</v>
       </c>
       <c r="B45" t="n">
-        <v>57826</v>
+        <v>97791</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5746,10 +5765,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>506984</v>
+        <v>507176</v>
       </c>
       <c r="R45" t="n">
-        <v>7032983</v>
+        <v>7032962</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5784,38 +5803,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5964,10 +5964,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130107359</v>
+        <v>130108121</v>
       </c>
       <c r="B47" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5975,34 +5975,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507226</v>
+        <v>506981</v>
       </c>
       <c r="R47" t="n">
-        <v>7032851</v>
+        <v>7032960</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6039,7 +6047,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6050,6 +6058,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6182,10 +6210,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130108121</v>
+        <v>130107359</v>
       </c>
       <c r="B49" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6193,42 +6221,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506981</v>
+        <v>507226</v>
       </c>
       <c r="R49" t="n">
-        <v>7032960</v>
+        <v>7032851</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6265,7 +6285,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6276,26 +6296,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6312,10 +6312,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130107319</v>
+        <v>130107309</v>
       </c>
       <c r="B50" t="n">
-        <v>97791</v>
+        <v>80314</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6323,27 +6323,30 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6351,10 +6354,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507144</v>
+        <v>507227</v>
       </c>
       <c r="R50" t="n">
-        <v>7033068</v>
+        <v>7032981</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6389,6 +6392,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På en sälg i granskog.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6402,6 +6410,26 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6419,41 +6447,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130107309</v>
+        <v>130108114</v>
       </c>
       <c r="B51" t="n">
-        <v>80314</v>
+        <v>83158</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6461,10 +6485,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507227</v>
+        <v>507064</v>
       </c>
       <c r="R51" t="n">
-        <v>7032981</v>
+        <v>7032974</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6499,11 +6523,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På en sälg i granskog.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6514,29 +6533,19 @@
       <c r="AG51" t="b">
         <v>0</v>
       </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6554,10 +6563,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130108114</v>
+        <v>130108122</v>
       </c>
       <c r="B52" t="n">
-        <v>83158</v>
+        <v>57826</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6565,26 +6574,31 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6592,10 +6606,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507064</v>
+        <v>506980</v>
       </c>
       <c r="R52" t="n">
-        <v>7032974</v>
+        <v>7032966</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6630,15 +6644,24 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
@@ -6670,42 +6693,38 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130108122</v>
+        <v>130107319</v>
       </c>
       <c r="B53" t="n">
-        <v>57826</v>
+        <v>97791</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6713,10 +6732,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>506980</v>
+        <v>507144</v>
       </c>
       <c r="R53" t="n">
-        <v>7032966</v>
+        <v>7033068</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6751,38 +6770,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>

--- a/artfynd/A 56557-2025 artfynd.xlsx
+++ b/artfynd/A 56557-2025 artfynd.xlsx
@@ -675,38 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130107316</v>
+        <v>130108125</v>
       </c>
       <c r="B2" t="n">
-        <v>97791</v>
+        <v>57826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507075</v>
+        <v>506976</v>
       </c>
       <c r="R2" t="n">
-        <v>7033179</v>
+        <v>7032983</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +756,43 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -782,42 +810,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130108125</v>
+        <v>130107316</v>
       </c>
       <c r="B3" t="n">
-        <v>57826</v>
+        <v>97791</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506976</v>
+        <v>507075</v>
       </c>
       <c r="R3" t="n">
-        <v>7032983</v>
+        <v>7033179</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,43 +887,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130108117</v>
+        <v>130107360</v>
       </c>
       <c r="B4" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,31 +928,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -960,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507057</v>
+        <v>507211</v>
       </c>
       <c r="R4" t="n">
-        <v>7032982</v>
+        <v>7032876</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +995,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,12 +1004,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1027,9 +1023,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1149,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130107360</v>
+        <v>130108117</v>
       </c>
       <c r="B6" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,26 +1161,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1187,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507211</v>
+        <v>507057</v>
       </c>
       <c r="R6" t="n">
-        <v>7032876</v>
+        <v>7032982</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1233,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,13 +1242,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1255,14 +1260,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130107373</v>
+        <v>130108119</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,34 +1291,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507202</v>
+        <v>506988</v>
       </c>
       <c r="R7" t="n">
-        <v>7033195</v>
+        <v>7032934</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1363,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran i äldre flersktad granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,6 +1374,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1382,10 +1410,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130108119</v>
+        <v>130107373</v>
       </c>
       <c r="B8" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,42 +1421,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506988</v>
+        <v>507202</v>
       </c>
       <c r="R8" t="n">
-        <v>7032934</v>
+        <v>7033195</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1465,7 +1485,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran i äldre flersktad granskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,26 +1496,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1512,7 +1512,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130107363</v>
+        <v>130107369</v>
       </c>
       <c r="B9" t="n">
         <v>79180</v>
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507069</v>
+        <v>507237</v>
       </c>
       <c r="R9" t="n">
-        <v>7033199</v>
+        <v>7033036</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1614,7 +1614,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130108131</v>
+        <v>130107363</v>
       </c>
       <c r="B10" t="n">
         <v>79180</v>
@@ -1643,19 +1643,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506958</v>
+        <v>507069</v>
       </c>
       <c r="R10" t="n">
-        <v>7032984</v>
+        <v>7033199</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1690,30 +1687,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1730,7 +1716,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130107369</v>
+        <v>130108131</v>
       </c>
       <c r="B11" t="n">
         <v>79180</v>
@@ -1759,16 +1745,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507237</v>
+        <v>506958</v>
       </c>
       <c r="R11" t="n">
-        <v>7033036</v>
+        <v>7032984</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1803,19 +1792,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -2327,10 +2327,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130108126</v>
+        <v>130107366</v>
       </c>
       <c r="B16" t="n">
-        <v>57985</v>
+        <v>79180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2338,50 +2338,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507059</v>
+        <v>507149</v>
       </c>
       <c r="R16" t="n">
-        <v>7032796</v>
+        <v>7033155</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2416,6 +2400,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2424,11 +2413,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2445,10 +2429,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130107366</v>
+        <v>130108115</v>
       </c>
       <c r="B17" t="n">
-        <v>79180</v>
+        <v>83158</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2456,34 +2440,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507149</v>
+        <v>506966</v>
       </c>
       <c r="R17" t="n">
-        <v>7033155</v>
+        <v>7032974</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2518,19 +2505,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2547,10 +2545,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130108127</v>
+        <v>130108126</v>
       </c>
       <c r="B18" t="n">
-        <v>80285</v>
+        <v>57985</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2558,37 +2556,50 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507051</v>
+        <v>507059</v>
       </c>
       <c r="R18" t="n">
-        <v>7032835</v>
+        <v>7032796</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2629,28 +2640,12 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2668,10 +2663,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130108115</v>
+        <v>130108127</v>
       </c>
       <c r="B19" t="n">
-        <v>83158</v>
+        <v>80285</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2679,21 +2674,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2706,10 +2701,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506966</v>
+        <v>507051</v>
       </c>
       <c r="R19" t="n">
-        <v>7032974</v>
+        <v>7032835</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2754,19 +2749,24 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3361,10 +3361,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130108129</v>
+        <v>130107324</v>
       </c>
       <c r="B25" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3372,26 +3372,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3399,10 +3403,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507068</v>
+        <v>507238</v>
       </c>
       <c r="R25" t="n">
-        <v>7032840</v>
+        <v>7032941</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3437,6 +3441,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>I riklig mängd på en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3454,17 +3463,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3482,10 +3496,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130107324</v>
+        <v>130108129</v>
       </c>
       <c r="B26" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3493,30 +3507,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3524,10 +3534,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507238</v>
+        <v>507068</v>
       </c>
       <c r="R26" t="n">
-        <v>7032941</v>
+        <v>7032840</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3562,11 +3572,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>I riklig mängd på en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3584,22 +3589,17 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3617,37 +3617,41 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130108128</v>
+        <v>130107327</v>
       </c>
       <c r="B27" t="n">
-        <v>78192</v>
+        <v>80321</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3655,10 +3659,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507058</v>
+        <v>507239</v>
       </c>
       <c r="R27" t="n">
-        <v>7032972</v>
+        <v>7032943</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3693,6 +3697,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På en gammal lunglavssälg.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3703,19 +3712,24 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3733,10 +3747,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130107362</v>
+        <v>130107310</v>
       </c>
       <c r="B28" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3744,34 +3758,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507201</v>
+        <v>507084</v>
       </c>
       <c r="R28" t="n">
-        <v>7032984</v>
+        <v>7033149</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3808,7 +3826,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rejäla hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3819,6 +3837,31 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3835,10 +3878,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130107310</v>
+        <v>130107362</v>
       </c>
       <c r="B29" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3846,38 +3889,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>507084</v>
+        <v>507201</v>
       </c>
       <c r="R29" t="n">
-        <v>7033149</v>
+        <v>7032984</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3914,7 +3953,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3925,31 +3964,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4170,41 +4184,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130107327</v>
+        <v>130108128</v>
       </c>
       <c r="B32" t="n">
-        <v>80321</v>
+        <v>78192</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>228579</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4212,10 +4222,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>507239</v>
+        <v>507058</v>
       </c>
       <c r="R32" t="n">
-        <v>7032943</v>
+        <v>7032972</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4250,11 +4260,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På en gammal lunglavssälg.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4265,24 +4270,19 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4430,10 +4430,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130107358</v>
+        <v>130108124</v>
       </c>
       <c r="B34" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4441,34 +4441,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507233</v>
+        <v>506973</v>
       </c>
       <c r="R34" t="n">
-        <v>7032821</v>
+        <v>7032980</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4505,7 +4513,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4516,6 +4524,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4532,10 +4560,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130108116</v>
+        <v>130107358</v>
       </c>
       <c r="B35" t="n">
-        <v>83158</v>
+        <v>79180</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4543,37 +4571,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506959</v>
+        <v>507233</v>
       </c>
       <c r="R35" t="n">
-        <v>7032984</v>
+        <v>7032821</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4608,30 +4633,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4648,10 +4662,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130108124</v>
+        <v>130108116</v>
       </c>
       <c r="B36" t="n">
-        <v>57826</v>
+        <v>83158</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4659,31 +4673,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4691,10 +4700,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506973</v>
+        <v>506959</v>
       </c>
       <c r="R36" t="n">
-        <v>7032980</v>
+        <v>7032984</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4729,24 +4738,15 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130107315</v>
+        <v>130107314</v>
       </c>
       <c r="B44" t="n">
         <v>97791</v>
@@ -5658,10 +5658,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507217</v>
+        <v>507176</v>
       </c>
       <c r="R44" t="n">
-        <v>7033002</v>
+        <v>7032962</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5726,7 +5726,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130107314</v>
+        <v>130107315</v>
       </c>
       <c r="B45" t="n">
         <v>97791</v>
@@ -5765,10 +5765,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>507176</v>
+        <v>507217</v>
       </c>
       <c r="R45" t="n">
-        <v>7032962</v>
+        <v>7033002</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6094,7 +6094,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130108130</v>
+        <v>130107359</v>
       </c>
       <c r="B48" t="n">
         <v>79180</v>
@@ -6123,19 +6123,16 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506954</v>
+        <v>507226</v>
       </c>
       <c r="R48" t="n">
-        <v>7033030</v>
+        <v>7032851</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6170,30 +6167,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6210,7 +6196,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130107359</v>
+        <v>130108130</v>
       </c>
       <c r="B49" t="n">
         <v>79180</v>
@@ -6239,16 +6225,19 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>507226</v>
+        <v>506954</v>
       </c>
       <c r="R49" t="n">
-        <v>7032851</v>
+        <v>7033030</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6283,19 +6272,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6447,10 +6447,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130108114</v>
+        <v>130108122</v>
       </c>
       <c r="B51" t="n">
-        <v>83158</v>
+        <v>57826</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6458,26 +6458,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6485,10 +6490,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507064</v>
+        <v>506980</v>
       </c>
       <c r="R51" t="n">
-        <v>7032974</v>
+        <v>7032966</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6523,15 +6528,24 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
@@ -6563,10 +6577,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130108122</v>
+        <v>130108114</v>
       </c>
       <c r="B52" t="n">
-        <v>57826</v>
+        <v>83158</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6574,31 +6588,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6606,10 +6615,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>506980</v>
+        <v>507064</v>
       </c>
       <c r="R52" t="n">
-        <v>7032966</v>
+        <v>7032974</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6644,24 +6653,15 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>

--- a/artfynd/A 56557-2025 artfynd.xlsx
+++ b/artfynd/A 56557-2025 artfynd.xlsx
@@ -1280,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130108119</v>
+        <v>130107373</v>
       </c>
       <c r="B7" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,42 +1291,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506988</v>
+        <v>507202</v>
       </c>
       <c r="R7" t="n">
-        <v>7032934</v>
+        <v>7033195</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1363,7 +1355,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran i äldre flersktad granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,26 +1366,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1410,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130107373</v>
+        <v>130108119</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,34 +1393,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507202</v>
+        <v>506988</v>
       </c>
       <c r="R8" t="n">
-        <v>7033195</v>
+        <v>7032934</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1485,7 +1465,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran i äldre flersktad granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1496,6 +1476,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -4430,42 +4430,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130108124</v>
+        <v>130107318</v>
       </c>
       <c r="B34" t="n">
-        <v>57826</v>
+        <v>97791</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4473,10 +4469,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506973</v>
+        <v>507226</v>
       </c>
       <c r="R34" t="n">
-        <v>7032980</v>
+        <v>7033130</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4511,38 +4507,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4560,38 +4537,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130107318</v>
+        <v>130108124</v>
       </c>
       <c r="B35" t="n">
-        <v>97791</v>
+        <v>57826</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4599,10 +4580,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>507226</v>
+        <v>506973</v>
       </c>
       <c r="R35" t="n">
-        <v>7033130</v>
+        <v>7032980</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4637,19 +4618,38 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4885,10 +4885,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130107367</v>
+        <v>130107325</v>
       </c>
       <c r="B38" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4896,34 +4896,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507157</v>
+        <v>507225</v>
       </c>
       <c r="R38" t="n">
-        <v>7033174</v>
+        <v>7033115</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4960,7 +4963,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4969,8 +4972,34 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4987,10 +5016,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130107325</v>
+        <v>130108118</v>
       </c>
       <c r="B39" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4998,26 +5027,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5025,10 +5059,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507225</v>
+        <v>506992</v>
       </c>
       <c r="R39" t="n">
-        <v>7033115</v>
+        <v>7032926</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5065,7 +5099,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5074,33 +5108,27 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5118,10 +5146,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130108118</v>
+        <v>130107367</v>
       </c>
       <c r="B40" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5129,42 +5157,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506992</v>
+        <v>507157</v>
       </c>
       <c r="R40" t="n">
-        <v>7032926</v>
+        <v>7033174</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5201,7 +5221,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5212,26 +5232,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -6066,10 +6066,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130108130</v>
+        <v>130108121</v>
       </c>
       <c r="B48" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6077,26 +6077,31 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6104,10 +6109,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506954</v>
+        <v>506981</v>
       </c>
       <c r="R48" t="n">
-        <v>7033030</v>
+        <v>7032960</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6142,15 +6147,24 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
@@ -6182,10 +6196,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130108121</v>
+        <v>130108130</v>
       </c>
       <c r="B49" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6193,31 +6207,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6225,10 +6234,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506981</v>
+        <v>506954</v>
       </c>
       <c r="R49" t="n">
-        <v>7032960</v>
+        <v>7033030</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6263,24 +6272,15 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -6312,40 +6312,39 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130108122</v>
+        <v>130107309</v>
       </c>
       <c r="B50" t="n">
-        <v>57826</v>
+        <v>80314</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -6355,10 +6354,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>506980</v>
+        <v>507227</v>
       </c>
       <c r="R50" t="n">
-        <v>7032966</v>
+        <v>7032981</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6395,7 +6394,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På en sälg i granskog.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6404,27 +6403,33 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6442,10 +6447,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130108114</v>
+        <v>130108122</v>
       </c>
       <c r="B51" t="n">
-        <v>83158</v>
+        <v>57826</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6453,26 +6458,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6480,10 +6490,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507064</v>
+        <v>506980</v>
       </c>
       <c r="R51" t="n">
-        <v>7032974</v>
+        <v>7032966</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6518,15 +6528,24 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
@@ -6558,41 +6577,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130107309</v>
+        <v>130108114</v>
       </c>
       <c r="B52" t="n">
-        <v>80314</v>
+        <v>83158</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6600,10 +6615,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507227</v>
+        <v>507064</v>
       </c>
       <c r="R52" t="n">
-        <v>7032981</v>
+        <v>7032974</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6638,11 +6653,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På en sälg i granskog.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6653,29 +6663,19 @@
       <c r="AG52" t="b">
         <v>0</v>
       </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>

--- a/artfynd/A 56557-2025 artfynd.xlsx
+++ b/artfynd/A 56557-2025 artfynd.xlsx
@@ -1280,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130107373</v>
+        <v>130108119</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,34 +1291,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507202</v>
+        <v>506988</v>
       </c>
       <c r="R7" t="n">
-        <v>7033195</v>
+        <v>7032934</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1363,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran i äldre flersktad granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,6 +1374,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1382,10 +1410,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130108119</v>
+        <v>130107373</v>
       </c>
       <c r="B8" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,42 +1421,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506988</v>
+        <v>507202</v>
       </c>
       <c r="R8" t="n">
-        <v>7032934</v>
+        <v>7033195</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1465,7 +1485,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran i äldre flersktad granskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,26 +1496,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -2327,10 +2327,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130108126</v>
+        <v>130107366</v>
       </c>
       <c r="B16" t="n">
-        <v>57985</v>
+        <v>79180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2338,50 +2338,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507059</v>
+        <v>507149</v>
       </c>
       <c r="R16" t="n">
-        <v>7032796</v>
+        <v>7033155</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2416,6 +2400,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2424,11 +2413,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2445,10 +2429,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130108127</v>
+        <v>130108115</v>
       </c>
       <c r="B17" t="n">
-        <v>80285</v>
+        <v>83158</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2456,21 +2440,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2483,10 +2467,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507051</v>
+        <v>506966</v>
       </c>
       <c r="R17" t="n">
-        <v>7032835</v>
+        <v>7032974</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2531,24 +2515,19 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2566,10 +2545,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130108115</v>
+        <v>130108127</v>
       </c>
       <c r="B18" t="n">
-        <v>83158</v>
+        <v>80285</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2577,21 +2556,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2604,10 +2583,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506966</v>
+        <v>507051</v>
       </c>
       <c r="R18" t="n">
-        <v>7032974</v>
+        <v>7032835</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2652,19 +2631,24 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2682,10 +2666,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130107366</v>
+        <v>130108126</v>
       </c>
       <c r="B19" t="n">
-        <v>79180</v>
+        <v>57985</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2693,34 +2677,50 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507149</v>
+        <v>507059</v>
       </c>
       <c r="R19" t="n">
-        <v>7033155</v>
+        <v>7032796</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2755,11 +2755,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2768,6 +2763,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2891,7 +2891,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130107370</v>
+        <v>130107332</v>
       </c>
       <c r="B21" t="n">
         <v>79180</v>
@@ -2920,19 +2920,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507211</v>
+        <v>507011</v>
       </c>
       <c r="R21" t="n">
-        <v>7033009</v>
+        <v>7033080</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2969,7 +2966,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2978,34 +2975,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3022,7 +2993,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130107332</v>
+        <v>130107370</v>
       </c>
       <c r="B22" t="n">
         <v>79180</v>
@@ -3051,16 +3022,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507011</v>
+        <v>507211</v>
       </c>
       <c r="R22" t="n">
-        <v>7033080</v>
+        <v>7033009</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3097,7 +3071,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3106,8 +3080,34 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -4430,38 +4430,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130107318</v>
+        <v>130108124</v>
       </c>
       <c r="B34" t="n">
-        <v>97791</v>
+        <v>57826</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4469,10 +4473,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507226</v>
+        <v>506973</v>
       </c>
       <c r="R34" t="n">
-        <v>7033130</v>
+        <v>7032980</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4507,19 +4511,38 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4537,42 +4560,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130108124</v>
+        <v>130107318</v>
       </c>
       <c r="B35" t="n">
-        <v>57826</v>
+        <v>97791</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4580,10 +4599,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506973</v>
+        <v>507226</v>
       </c>
       <c r="R35" t="n">
-        <v>7032980</v>
+        <v>7033130</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4618,38 +4637,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4885,10 +4885,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130107325</v>
+        <v>130107367</v>
       </c>
       <c r="B38" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4896,37 +4896,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507225</v>
+        <v>507157</v>
       </c>
       <c r="R38" t="n">
-        <v>7033115</v>
+        <v>7033174</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4963,7 +4960,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4972,34 +4969,8 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5016,10 +4987,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130108118</v>
+        <v>130107325</v>
       </c>
       <c r="B39" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5027,31 +4998,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5059,10 +5025,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506992</v>
+        <v>507225</v>
       </c>
       <c r="R39" t="n">
-        <v>7032926</v>
+        <v>7033115</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5099,7 +5065,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5108,27 +5074,33 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5146,10 +5118,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130107367</v>
+        <v>130108118</v>
       </c>
       <c r="B40" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5157,34 +5129,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507157</v>
+        <v>506992</v>
       </c>
       <c r="R40" t="n">
-        <v>7033174</v>
+        <v>7032926</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5221,7 +5201,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5232,6 +5212,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -6066,10 +6066,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130108121</v>
+        <v>130108130</v>
       </c>
       <c r="B48" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6077,31 +6077,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6109,10 +6104,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506981</v>
+        <v>506954</v>
       </c>
       <c r="R48" t="n">
-        <v>7032960</v>
+        <v>7033030</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6147,24 +6142,15 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
@@ -6196,10 +6182,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130108130</v>
+        <v>130108121</v>
       </c>
       <c r="B49" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6207,26 +6193,31 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6234,10 +6225,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506954</v>
+        <v>506981</v>
       </c>
       <c r="R49" t="n">
-        <v>7033030</v>
+        <v>7032960</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6272,15 +6263,24 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -6312,39 +6312,40 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130107309</v>
+        <v>130108122</v>
       </c>
       <c r="B50" t="n">
-        <v>80314</v>
+        <v>57826</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -6354,10 +6355,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507227</v>
+        <v>506980</v>
       </c>
       <c r="R50" t="n">
-        <v>7032981</v>
+        <v>7032966</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6394,7 +6395,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På en sälg i granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6403,33 +6404,27 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6447,10 +6442,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130108122</v>
+        <v>130108114</v>
       </c>
       <c r="B51" t="n">
-        <v>57826</v>
+        <v>83158</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6458,31 +6453,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6490,10 +6480,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506980</v>
+        <v>507064</v>
       </c>
       <c r="R51" t="n">
-        <v>7032966</v>
+        <v>7032974</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6528,24 +6518,15 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
@@ -6577,37 +6558,41 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130108114</v>
+        <v>130107309</v>
       </c>
       <c r="B52" t="n">
-        <v>83158</v>
+        <v>80314</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6615,10 +6600,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507064</v>
+        <v>507227</v>
       </c>
       <c r="R52" t="n">
-        <v>7032974</v>
+        <v>7032981</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6653,6 +6638,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På en sälg i granskog.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6663,19 +6653,29 @@
       <c r="AG52" t="b">
         <v>0</v>
       </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>

--- a/artfynd/A 56557-2025 artfynd.xlsx
+++ b/artfynd/A 56557-2025 artfynd.xlsx
@@ -675,38 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130107316</v>
+        <v>130108125</v>
       </c>
       <c r="B2" t="n">
-        <v>97791</v>
+        <v>57826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507075</v>
+        <v>506976</v>
       </c>
       <c r="R2" t="n">
-        <v>7033179</v>
+        <v>7032983</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +756,43 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -782,42 +810,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130108125</v>
+        <v>130107316</v>
       </c>
       <c r="B3" t="n">
-        <v>57826</v>
+        <v>97791</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506976</v>
+        <v>507075</v>
       </c>
       <c r="R3" t="n">
-        <v>7032983</v>
+        <v>7033179</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,43 +887,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130107366</v>
+        <v>130108126</v>
       </c>
       <c r="B16" t="n">
-        <v>79180</v>
+        <v>57985</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2338,34 +2338,50 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507149</v>
+        <v>507059</v>
       </c>
       <c r="R16" t="n">
-        <v>7033155</v>
+        <v>7032796</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2400,11 +2416,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2413,6 +2424,11 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2429,10 +2445,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130108115</v>
+        <v>130108127</v>
       </c>
       <c r="B17" t="n">
-        <v>83158</v>
+        <v>80285</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,21 +2456,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2467,10 +2483,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506966</v>
+        <v>507051</v>
       </c>
       <c r="R17" t="n">
-        <v>7032974</v>
+        <v>7032835</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2515,19 +2531,24 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2545,10 +2566,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130108127</v>
+        <v>130108115</v>
       </c>
       <c r="B18" t="n">
-        <v>80285</v>
+        <v>83158</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2556,21 +2577,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2583,10 +2604,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>507051</v>
+        <v>506966</v>
       </c>
       <c r="R18" t="n">
-        <v>7032835</v>
+        <v>7032974</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2631,24 +2652,19 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2666,10 +2682,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130108126</v>
+        <v>130107366</v>
       </c>
       <c r="B19" t="n">
-        <v>57985</v>
+        <v>79180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,50 +2693,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507059</v>
+        <v>507149</v>
       </c>
       <c r="R19" t="n">
-        <v>7032796</v>
+        <v>7033155</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2755,6 +2755,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2763,11 +2768,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2891,7 +2891,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130107332</v>
+        <v>130107370</v>
       </c>
       <c r="B21" t="n">
         <v>79180</v>
@@ -2920,16 +2920,19 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507011</v>
+        <v>507211</v>
       </c>
       <c r="R21" t="n">
-        <v>7033080</v>
+        <v>7033009</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2966,7 +2969,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2975,8 +2978,34 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2993,7 +3022,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130107370</v>
+        <v>130107332</v>
       </c>
       <c r="B22" t="n">
         <v>79180</v>
@@ -3022,19 +3051,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507211</v>
+        <v>507011</v>
       </c>
       <c r="R22" t="n">
-        <v>7033009</v>
+        <v>7033080</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3071,7 +3097,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3080,34 +3106,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -4430,42 +4430,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130108124</v>
+        <v>130107318</v>
       </c>
       <c r="B34" t="n">
-        <v>57826</v>
+        <v>97791</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4473,10 +4469,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506973</v>
+        <v>507226</v>
       </c>
       <c r="R34" t="n">
-        <v>7032980</v>
+        <v>7033130</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4511,38 +4507,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4560,38 +4537,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130107318</v>
+        <v>130108124</v>
       </c>
       <c r="B35" t="n">
-        <v>97791</v>
+        <v>57826</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4599,10 +4580,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>507226</v>
+        <v>506973</v>
       </c>
       <c r="R35" t="n">
-        <v>7033130</v>
+        <v>7032980</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4637,19 +4618,38 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>

--- a/artfynd/A 56557-2025 artfynd.xlsx
+++ b/artfynd/A 56557-2025 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>130107316</v>
       </c>
       <c r="B3" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130107371</v>
+        <v>130107360</v>
       </c>
       <c r="B4" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -946,16 +946,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507222</v>
+        <v>507211</v>
       </c>
       <c r="R4" t="n">
-        <v>7033039</v>
+        <v>7032876</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +995,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,8 +1004,34 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1019,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130107360</v>
+        <v>130107371</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,19 +1077,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507211</v>
+        <v>507222</v>
       </c>
       <c r="R5" t="n">
-        <v>7032876</v>
+        <v>7033039</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,7 +1123,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,34 +1132,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1280,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130108119</v>
+        <v>130107373</v>
       </c>
       <c r="B7" t="n">
-        <v>57826</v>
+        <v>79183</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,42 +1291,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506988</v>
+        <v>507202</v>
       </c>
       <c r="R7" t="n">
-        <v>7032934</v>
+        <v>7033195</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1363,7 +1355,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På gran i äldre flersktad granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,26 +1366,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1410,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130107373</v>
+        <v>130108119</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,34 +1393,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507202</v>
+        <v>506988</v>
       </c>
       <c r="R8" t="n">
-        <v>7033195</v>
+        <v>7032934</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1485,7 +1465,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gran i äldre flersktad granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1496,6 +1476,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1515,7 +1515,7 @@
         <v>130107369</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>130107363</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>130108131</v>
       </c>
       <c r="B11" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>130107374</v>
       </c>
       <c r="B12" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,48 +1934,61 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130107361</v>
+        <v>130107328</v>
       </c>
       <c r="B13" t="n">
-        <v>79180</v>
+        <v>57930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507236</v>
+        <v>507190</v>
       </c>
       <c r="R13" t="n">
-        <v>7032990</v>
+        <v>7033178</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,7 +2025,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2021,33 +2034,12 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2065,10 +2057,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130107307</v>
+        <v>130107361</v>
       </c>
       <c r="B14" t="n">
-        <v>57826</v>
+        <v>79183</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,46 +2068,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507225</v>
+        <v>507236</v>
       </c>
       <c r="R14" t="n">
-        <v>7033149</v>
+        <v>7032990</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2152,7 +2135,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,6 +2144,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2181,12 +2165,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2204,27 +2188,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130107328</v>
+        <v>130107307</v>
       </c>
       <c r="B15" t="n">
-        <v>57930</v>
+        <v>57826</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2232,16 +2216,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2255,10 +2235,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507190</v>
+        <v>507225</v>
       </c>
       <c r="R15" t="n">
-        <v>7033178</v>
+        <v>7033149</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2295,7 +2275,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
+          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2310,6 +2290,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130108126</v>
+        <v>130108127</v>
       </c>
       <c r="B16" t="n">
-        <v>57985</v>
+        <v>80288</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2338,50 +2338,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507059</v>
+        <v>507051</v>
       </c>
       <c r="R16" t="n">
-        <v>7032796</v>
+        <v>7032835</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2422,12 +2409,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2445,10 +2448,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130108127</v>
+        <v>130107366</v>
       </c>
       <c r="B17" t="n">
-        <v>80285</v>
+        <v>79183</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2456,37 +2459,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507051</v>
+        <v>507149</v>
       </c>
       <c r="R17" t="n">
-        <v>7032835</v>
+        <v>7033155</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2521,35 +2521,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2569,7 +2553,7 @@
         <v>130108115</v>
       </c>
       <c r="B18" t="n">
-        <v>83158</v>
+        <v>83161</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2682,10 +2666,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130107366</v>
+        <v>130108126</v>
       </c>
       <c r="B19" t="n">
-        <v>79180</v>
+        <v>57985</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2693,34 +2677,50 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507149</v>
+        <v>507059</v>
       </c>
       <c r="R19" t="n">
-        <v>7033155</v>
+        <v>7032796</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2755,11 +2755,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2768,6 +2763,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2787,7 +2787,7 @@
         <v>130107317</v>
       </c>
       <c r="B20" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2891,10 +2891,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130107370</v>
+        <v>130107332</v>
       </c>
       <c r="B21" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2920,19 +2920,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507211</v>
+        <v>507011</v>
       </c>
       <c r="R21" t="n">
-        <v>7033009</v>
+        <v>7033080</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2969,7 +2966,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2978,34 +2975,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3022,10 +2993,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130107332</v>
+        <v>130107370</v>
       </c>
       <c r="B22" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3051,16 +3022,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507011</v>
+        <v>507211</v>
       </c>
       <c r="R22" t="n">
-        <v>7033080</v>
+        <v>7033009</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3097,7 +3071,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3106,8 +3080,34 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3127,7 +3127,7 @@
         <v>130107329</v>
       </c>
       <c r="B23" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>130107364</v>
       </c>
       <c r="B24" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>130108129</v>
       </c>
       <c r="B25" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>130107324</v>
       </c>
       <c r="B26" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3617,10 +3617,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130107362</v>
+        <v>130108128</v>
       </c>
       <c r="B27" t="n">
-        <v>79180</v>
+        <v>78195</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3628,34 +3628,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507201</v>
+        <v>507058</v>
       </c>
       <c r="R27" t="n">
-        <v>7032984</v>
+        <v>7032972</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3690,19 +3693,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3719,45 +3733,52 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130107365</v>
+        <v>130107327</v>
       </c>
       <c r="B28" t="n">
-        <v>79180</v>
+        <v>80324</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507106</v>
+        <v>507239</v>
       </c>
       <c r="R28" t="n">
-        <v>7033205</v>
+        <v>7032943</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3794,7 +3815,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På en gammal lunglavssälg.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3803,8 +3824,29 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3821,10 +3863,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130107368</v>
+        <v>130107310</v>
       </c>
       <c r="B29" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3832,34 +3874,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>507204</v>
+        <v>507084</v>
       </c>
       <c r="R29" t="n">
-        <v>7033154</v>
+        <v>7033149</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3896,7 +3942,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rejäla hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3907,6 +3953,31 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3923,52 +3994,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130107327</v>
+        <v>130107362</v>
       </c>
       <c r="B30" t="n">
-        <v>80321</v>
+        <v>79183</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>507239</v>
+        <v>507201</v>
       </c>
       <c r="R30" t="n">
-        <v>7032943</v>
+        <v>7032984</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4005,7 +4069,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På en gammal lunglavssälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4014,29 +4078,8 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4053,10 +4096,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130107310</v>
+        <v>130107365</v>
       </c>
       <c r="B31" t="n">
-        <v>57823</v>
+        <v>79183</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4064,38 +4107,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507084</v>
+        <v>507106</v>
       </c>
       <c r="R31" t="n">
-        <v>7033149</v>
+        <v>7033205</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4132,7 +4171,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4143,31 +4182,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4184,10 +4198,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130108128</v>
+        <v>130107368</v>
       </c>
       <c r="B32" t="n">
-        <v>78192</v>
+        <v>79183</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4195,37 +4209,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>507058</v>
+        <v>507204</v>
       </c>
       <c r="R32" t="n">
-        <v>7032972</v>
+        <v>7033154</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4260,30 +4271,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4433,7 +4433,7 @@
         <v>130107318</v>
       </c>
       <c r="B34" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4537,10 +4537,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130108124</v>
+        <v>130107358</v>
       </c>
       <c r="B35" t="n">
-        <v>57826</v>
+        <v>79183</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4548,42 +4548,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506973</v>
+        <v>507233</v>
       </c>
       <c r="R35" t="n">
-        <v>7032980</v>
+        <v>7032821</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4620,7 +4612,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4631,26 +4623,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4670,7 +4642,7 @@
         <v>130108116</v>
       </c>
       <c r="B36" t="n">
-        <v>83158</v>
+        <v>83161</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4783,10 +4755,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130107358</v>
+        <v>130108124</v>
       </c>
       <c r="B37" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4794,34 +4766,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>507233</v>
+        <v>506973</v>
       </c>
       <c r="R37" t="n">
-        <v>7032821</v>
+        <v>7032980</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4858,7 +4838,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4869,6 +4849,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4888,7 +4888,7 @@
         <v>130107367</v>
       </c>
       <c r="B38" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4987,10 +4987,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130107325</v>
+        <v>130108118</v>
       </c>
       <c r="B39" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4998,26 +4998,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5025,10 +5030,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>507225</v>
+        <v>506992</v>
       </c>
       <c r="R39" t="n">
-        <v>7033115</v>
+        <v>7032926</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5065,7 +5070,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5074,33 +5079,27 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5118,10 +5117,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130108118</v>
+        <v>130107325</v>
       </c>
       <c r="B40" t="n">
-        <v>57826</v>
+        <v>80288</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5129,31 +5128,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5161,10 +5155,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>506992</v>
+        <v>507225</v>
       </c>
       <c r="R40" t="n">
-        <v>7032926</v>
+        <v>7033115</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5201,7 +5195,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5210,27 +5204,33 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5251,7 +5251,7 @@
         <v>130107372</v>
       </c>
       <c r="B41" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
         <v>130107314</v>
       </c>
       <c r="B44" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>130107315</v>
       </c>
       <c r="B45" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>130107331</v>
       </c>
       <c r="B46" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>130107359</v>
       </c>
       <c r="B47" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>130108130</v>
       </c>
       <c r="B48" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6312,10 +6312,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130108122</v>
+        <v>130108114</v>
       </c>
       <c r="B50" t="n">
-        <v>57826</v>
+        <v>83161</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6323,31 +6323,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6355,10 +6350,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>506980</v>
+        <v>507064</v>
       </c>
       <c r="R50" t="n">
-        <v>7032966</v>
+        <v>7032974</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6393,24 +6388,15 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -6442,10 +6428,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130108114</v>
+        <v>130108122</v>
       </c>
       <c r="B51" t="n">
-        <v>83158</v>
+        <v>57826</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6453,26 +6439,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6480,10 +6471,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>507064</v>
+        <v>506980</v>
       </c>
       <c r="R51" t="n">
-        <v>7032974</v>
+        <v>7032966</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6518,15 +6509,24 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>130107309</v>
       </c>
       <c r="B52" t="n">
-        <v>80314</v>
+        <v>80317</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>130107319</v>
       </c>
       <c r="B53" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 56557-2025 artfynd.xlsx
+++ b/artfynd/A 56557-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130108125</v>
+        <v>130107329</v>
       </c>
       <c r="B2" t="n">
-        <v>57826</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,29 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506976</v>
+        <v>507152</v>
       </c>
       <c r="R2" t="n">
-        <v>7032983</v>
+        <v>7033148</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +757,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Flera fruktkroppar i en levande gran med sockelbildning.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,12 +766,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -810,49 +810,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130107316</v>
+        <v>130107332</v>
       </c>
       <c r="B3" t="n">
-        <v>97794</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507075</v>
+        <v>507011</v>
       </c>
       <c r="R3" t="n">
-        <v>7033179</v>
+        <v>7033080</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,20 +883,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -917,14 +912,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130107360</v>
+        <v>130107338</v>
       </c>
       <c r="B4" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -946,19 +941,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507211</v>
+        <v>507073</v>
       </c>
       <c r="R4" t="n">
-        <v>7032876</v>
+        <v>7032765</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +987,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,34 +996,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1048,14 +1014,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130107371</v>
+        <v>130107339</v>
       </c>
       <c r="B5" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1077,16 +1043,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507222</v>
+        <v>507154</v>
       </c>
       <c r="R5" t="n">
-        <v>7033039</v>
+        <v>7032764</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,7 +1092,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en stående död granhögstubbe.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,8 +1101,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1150,53 +1145,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130108117</v>
+        <v>130107358</v>
       </c>
       <c r="B6" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507057</v>
+        <v>507233</v>
       </c>
       <c r="R6" t="n">
-        <v>7032982</v>
+        <v>7032821</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1220,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,26 +1231,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1280,14 +1247,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130107373</v>
+        <v>130107359</v>
       </c>
       <c r="B7" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1315,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507202</v>
+        <v>507226</v>
       </c>
       <c r="R7" t="n">
-        <v>7033195</v>
+        <v>7032851</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1322,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran i äldre flersktad granskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,42 +1349,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130108119</v>
+        <v>130107360</v>
       </c>
       <c r="B8" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1425,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506988</v>
+        <v>507211</v>
       </c>
       <c r="R8" t="n">
-        <v>7032934</v>
+        <v>7032876</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1465,7 +1427,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,12 +1436,13 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1492,9 +1455,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1512,14 +1480,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130107369</v>
+        <v>130107361</v>
       </c>
       <c r="B9" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1541,16 +1509,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507237</v>
+        <v>507236</v>
       </c>
       <c r="R9" t="n">
-        <v>7033036</v>
+        <v>7032990</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1587,7 +1558,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,8 +1567,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1614,14 +1611,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130107363</v>
+        <v>130107362</v>
       </c>
       <c r="B10" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1649,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507069</v>
+        <v>507201</v>
       </c>
       <c r="R10" t="n">
-        <v>7033199</v>
+        <v>7032984</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1716,14 +1713,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130108131</v>
+        <v>130107363</v>
       </c>
       <c r="B11" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1745,19 +1742,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506958</v>
+        <v>507069</v>
       </c>
       <c r="R11" t="n">
-        <v>7032984</v>
+        <v>7033199</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,30 +1786,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1832,14 +1815,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130107374</v>
+        <v>130107364</v>
       </c>
       <c r="B12" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1867,10 +1850,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507101</v>
+        <v>507091</v>
       </c>
       <c r="R12" t="n">
-        <v>7033240</v>
+        <v>7033218</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1890,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,61 +1917,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130107328</v>
+        <v>130107365</v>
       </c>
       <c r="B13" t="n">
-        <v>57930</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507190</v>
+        <v>507106</v>
       </c>
       <c r="R13" t="n">
-        <v>7033178</v>
+        <v>7033205</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2025,7 +1992,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,11 +2003,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2057,14 +2019,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130107361</v>
+        <v>130107366</v>
       </c>
       <c r="B14" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2086,19 +2048,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507236</v>
+        <v>507149</v>
       </c>
       <c r="R14" t="n">
-        <v>7032990</v>
+        <v>7033155</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2135,7 +2094,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,34 +2103,8 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2188,57 +2121,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130107307</v>
+        <v>130107367</v>
       </c>
       <c r="B15" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507225</v>
+        <v>507157</v>
       </c>
       <c r="R15" t="n">
-        <v>7033149</v>
+        <v>7033174</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2275,7 +2196,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2286,31 +2207,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2327,48 +2223,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130108127</v>
+        <v>130107368</v>
       </c>
       <c r="B16" t="n">
-        <v>80288</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507051</v>
+        <v>507204</v>
       </c>
       <c r="R16" t="n">
-        <v>7032835</v>
+        <v>7033154</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2403,35 +2296,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2448,14 +2325,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130107366</v>
+        <v>130107369</v>
       </c>
       <c r="B17" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2483,10 +2360,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507149</v>
+        <v>507237</v>
       </c>
       <c r="R17" t="n">
-        <v>7033155</v>
+        <v>7033036</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2550,32 +2427,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130108115</v>
+        <v>130107370</v>
       </c>
       <c r="B18" t="n">
-        <v>83161</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2588,10 +2465,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506966</v>
+        <v>507211</v>
       </c>
       <c r="R18" t="n">
-        <v>7032974</v>
+        <v>7033009</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2626,6 +2503,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2636,6 +2518,11 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ18" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2646,9 +2533,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2666,61 +2558,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130108126</v>
+        <v>130107371</v>
       </c>
       <c r="B19" t="n">
-        <v>57985</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507059</v>
+        <v>507222</v>
       </c>
       <c r="R19" t="n">
-        <v>7032796</v>
+        <v>7033039</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2755,6 +2631,11 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2763,11 +2644,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2784,49 +2660,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130107317</v>
+        <v>130107372</v>
       </c>
       <c r="B20" t="n">
-        <v>97794</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507267</v>
+        <v>507223</v>
       </c>
       <c r="R20" t="n">
-        <v>7033117</v>
+        <v>7033198</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2861,20 +2733,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2891,14 +2762,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130107332</v>
+        <v>130107373</v>
       </c>
       <c r="B21" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2926,10 +2797,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507011</v>
+        <v>507202</v>
       </c>
       <c r="R21" t="n">
-        <v>7033080</v>
+        <v>7033195</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2966,7 +2837,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På gran i äldre flersktad granskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2993,14 +2864,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130107370</v>
+        <v>130107374</v>
       </c>
       <c r="B22" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3022,19 +2893,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507211</v>
+        <v>507101</v>
       </c>
       <c r="R22" t="n">
-        <v>7033009</v>
+        <v>7033240</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3071,7 +2939,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3080,34 +2948,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3124,41 +2966,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130107329</v>
+        <v>130108129</v>
       </c>
       <c r="B23" t="n">
-        <v>91727</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3166,10 +3004,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507152</v>
+        <v>507068</v>
       </c>
       <c r="R23" t="n">
-        <v>7033148</v>
+        <v>7032840</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3204,11 +3042,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en levande gran med sockelbildning.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3234,14 +3067,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3259,14 +3087,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130107364</v>
+        <v>130108130</v>
       </c>
       <c r="B24" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3288,16 +3116,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507091</v>
+        <v>506954</v>
       </c>
       <c r="R24" t="n">
-        <v>7033218</v>
+        <v>7033030</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3332,19 +3163,30 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gran.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3361,14 +3203,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130108129</v>
+        <v>130108131</v>
       </c>
       <c r="B25" t="n">
-        <v>79183</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3399,10 +3241,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507068</v>
+        <v>506958</v>
       </c>
       <c r="R25" t="n">
-        <v>7032840</v>
+        <v>7032984</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3446,11 +3288,6 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3482,10 +3319,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130107324</v>
+        <v>130108114</v>
       </c>
       <c r="B26" t="n">
-        <v>80288</v>
+        <v>83307</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3493,30 +3330,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3524,10 +3357,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507238</v>
+        <v>507064</v>
       </c>
       <c r="R26" t="n">
-        <v>7032941</v>
+        <v>7032974</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3562,11 +3395,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>I riklig mängd på en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3577,29 +3405,19 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3617,10 +3435,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130108128</v>
+        <v>130108115</v>
       </c>
       <c r="B27" t="n">
-        <v>78195</v>
+        <v>83307</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3628,21 +3446,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3655,10 +3473,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507058</v>
+        <v>506966</v>
       </c>
       <c r="R27" t="n">
-        <v>7032972</v>
+        <v>7032974</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3733,41 +3551,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130107327</v>
+        <v>130108116</v>
       </c>
       <c r="B28" t="n">
-        <v>80324</v>
+        <v>83307</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3775,10 +3589,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507239</v>
+        <v>506959</v>
       </c>
       <c r="R28" t="n">
-        <v>7032943</v>
+        <v>7032984</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3813,11 +3627,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På en gammal lunglavssälg.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3828,24 +3637,19 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3863,10 +3667,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130107310</v>
+        <v>130107324</v>
       </c>
       <c r="B29" t="n">
-        <v>57823</v>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3874,27 +3678,30 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3902,10 +3709,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>507084</v>
+        <v>507238</v>
       </c>
       <c r="R29" t="n">
-        <v>7033149</v>
+        <v>7032941</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3942,7 +3749,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en gran.</t>
+          <t>I riklig mängd på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3951,6 +3758,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3961,22 +3769,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3994,10 +3802,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130107362</v>
+        <v>130107325</v>
       </c>
       <c r="B30" t="n">
-        <v>79183</v>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4005,34 +3813,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>507201</v>
+        <v>507225</v>
       </c>
       <c r="R30" t="n">
-        <v>7032984</v>
+        <v>7033115</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4069,7 +3880,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4078,8 +3889,34 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4096,10 +3933,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130107365</v>
+        <v>130108127</v>
       </c>
       <c r="B31" t="n">
-        <v>79183</v>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4107,34 +3944,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>507106</v>
+        <v>507051</v>
       </c>
       <c r="R31" t="n">
-        <v>7033205</v>
+        <v>7032835</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4169,19 +4009,35 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4198,45 +4054,52 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130107368</v>
+        <v>130107309</v>
       </c>
       <c r="B32" t="n">
-        <v>79183</v>
+        <v>80461</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>507204</v>
+        <v>507227</v>
       </c>
       <c r="R32" t="n">
-        <v>7033154</v>
+        <v>7032981</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4273,7 +4136,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en sälg i granskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4282,8 +4145,34 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4300,40 +4189,39 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130108120</v>
+        <v>130107327</v>
       </c>
       <c r="B33" t="n">
-        <v>57826</v>
+        <v>80468</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4343,10 +4231,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506983</v>
+        <v>507239</v>
       </c>
       <c r="R33" t="n">
-        <v>7032942</v>
+        <v>7032943</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4383,7 +4271,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På en gammal lunglavssälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4392,27 +4280,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4430,10 +4319,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130107318</v>
+        <v>130107310</v>
       </c>
       <c r="B34" t="n">
-        <v>97794</v>
+        <v>57950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4441,27 +4330,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4469,10 +4358,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>507226</v>
+        <v>507084</v>
       </c>
       <c r="R34" t="n">
-        <v>7033130</v>
+        <v>7033149</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4507,19 +4396,43 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4537,10 +4450,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130107358</v>
+        <v>130107302</v>
       </c>
       <c r="B35" t="n">
-        <v>79183</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4548,34 +4461,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>507233</v>
+        <v>507075</v>
       </c>
       <c r="R35" t="n">
-        <v>7032821</v>
+        <v>7032759</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4612,7 +4533,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på stambasen av en gran vid en nybruten väg.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4623,6 +4544,31 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4639,10 +4585,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130108116</v>
+        <v>130107306</v>
       </c>
       <c r="B36" t="n">
-        <v>83161</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4650,37 +4596,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506959</v>
+        <v>507221</v>
       </c>
       <c r="R36" t="n">
-        <v>7032984</v>
+        <v>7033159</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4715,16 +4670,25 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack, enstaka färska och rejält med äldre, påtagligt och tydligt på en granstam.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AJ36" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4735,9 +4699,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4755,10 +4724,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130108124</v>
+        <v>130107307</v>
       </c>
       <c r="B37" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4788,20 +4757,24 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506973</v>
+        <v>507225</v>
       </c>
       <c r="R37" t="n">
-        <v>7032980</v>
+        <v>7033149</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4838,7 +4811,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska och äldre, på en gran nedanför en mindre sluttning. I området kring fyndplatsen finns partier med stående död ved av gran som indikerar både högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4852,7 +4825,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -4865,9 +4838,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4885,10 +4863,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130107367</v>
+        <v>130108117</v>
       </c>
       <c r="B38" t="n">
-        <v>79183</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4896,34 +4874,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>507157</v>
+        <v>507057</v>
       </c>
       <c r="R38" t="n">
-        <v>7033174</v>
+        <v>7032982</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4960,7 +4946,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4971,6 +4957,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4990,7 +4996,7 @@
         <v>130108118</v>
       </c>
       <c r="B39" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5117,10 +5123,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130107325</v>
+        <v>130108119</v>
       </c>
       <c r="B40" t="n">
-        <v>80288</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5128,26 +5134,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5155,10 +5166,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>507225</v>
+        <v>506988</v>
       </c>
       <c r="R40" t="n">
-        <v>7033115</v>
+        <v>7032934</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5195,7 +5206,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en grovbarkad gammal sälg.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5204,33 +5215,27 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5248,10 +5253,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130107372</v>
+        <v>130108120</v>
       </c>
       <c r="B41" t="n">
-        <v>79183</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5259,34 +5264,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>507223</v>
+        <v>506983</v>
       </c>
       <c r="R41" t="n">
-        <v>7033198</v>
+        <v>7032942</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5323,7 +5336,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5334,6 +5347,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5350,10 +5383,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130107306</v>
+        <v>130108121</v>
       </c>
       <c r="B42" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5383,24 +5416,20 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>507221</v>
+        <v>506981</v>
       </c>
       <c r="R42" t="n">
-        <v>7033159</v>
+        <v>7032960</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5437,7 +5466,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, enstaka färska och rejält med äldre, påtagligt och tydligt på en granstam.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5451,7 +5480,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -5464,14 +5493,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5489,10 +5513,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130108123</v>
+        <v>130108122</v>
       </c>
       <c r="B43" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5522,7 +5546,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5532,10 +5556,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>506984</v>
+        <v>506980</v>
       </c>
       <c r="R43" t="n">
-        <v>7032983</v>
+        <v>7032966</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5572,7 +5596,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5619,38 +5643,42 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130107314</v>
+        <v>130108123</v>
       </c>
       <c r="B44" t="n">
-        <v>97794</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5658,10 +5686,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>507176</v>
+        <v>506984</v>
       </c>
       <c r="R44" t="n">
-        <v>7032962</v>
+        <v>7032983</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5696,19 +5724,38 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5726,38 +5773,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130107315</v>
+        <v>130108124</v>
       </c>
       <c r="B45" t="n">
-        <v>97794</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5765,10 +5816,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>507217</v>
+        <v>506973</v>
       </c>
       <c r="R45" t="n">
-        <v>7033002</v>
+        <v>7032980</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5803,19 +5854,38 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5833,10 +5903,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130107331</v>
+        <v>130108125</v>
       </c>
       <c r="B46" t="n">
-        <v>91751</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5844,24 +5914,29 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -5871,10 +5946,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>507157</v>
+        <v>506976</v>
       </c>
       <c r="R46" t="n">
-        <v>7033090</v>
+        <v>7032983</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5911,7 +5986,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en granhögstubbe.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5920,13 +5995,12 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -5941,12 +6015,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5964,10 +6038,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130107359</v>
+        <v>130108126</v>
       </c>
       <c r="B47" t="n">
-        <v>79183</v>
+        <v>58114</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5975,34 +6049,50 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>507226</v>
+        <v>507059</v>
       </c>
       <c r="R47" t="n">
-        <v>7032851</v>
+        <v>7032796</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6037,11 +6127,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6050,6 +6135,11 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6066,10 +6156,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130108130</v>
+        <v>130107328</v>
       </c>
       <c r="B48" t="n">
-        <v>79183</v>
+        <v>58057</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6077,37 +6167,50 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Getsjöflon, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>506954</v>
+        <v>507190</v>
       </c>
       <c r="R48" t="n">
-        <v>7033030</v>
+        <v>7033178</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6142,29 +6245,23 @@
           <t>2025-12-06</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>1 lavskrika med lockläte sågs i gammal bitvis flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6182,42 +6279,38 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130108121</v>
+        <v>130107314</v>
       </c>
       <c r="B49" t="n">
-        <v>57826</v>
+        <v>97983</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6225,10 +6318,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>506981</v>
+        <v>507176</v>
       </c>
       <c r="R49" t="n">
-        <v>7032960</v>
+        <v>7032962</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6263,38 +6356,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6312,37 +6386,38 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130108114</v>
+        <v>130107315</v>
       </c>
       <c r="B50" t="n">
-        <v>83161</v>
+        <v>97983</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6350,10 +6425,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>507064</v>
+        <v>507217</v>
       </c>
       <c r="R50" t="n">
-        <v>7032974</v>
+        <v>7033002</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6398,19 +6473,9 @@
       <c r="AG50" t="b">
         <v>0</v>
       </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6428,42 +6493,38 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130108122</v>
+        <v>130107316</v>
       </c>
       <c r="B51" t="n">
-        <v>57826</v>
+        <v>97983</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6471,10 +6532,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>506980</v>
+        <v>507075</v>
       </c>
       <c r="R51" t="n">
-        <v>7032966</v>
+        <v>7033179</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6509,38 +6570,19 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6558,10 +6600,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130107309</v>
+        <v>130107317</v>
       </c>
       <c r="B52" t="n">
-        <v>80317</v>
+        <v>97983</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6569,30 +6611,27 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6600,10 +6639,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>507227</v>
+        <v>507267</v>
       </c>
       <c r="R52" t="n">
-        <v>7032981</v>
+        <v>7033117</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6638,11 +6677,6 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På en sälg i granskog.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6656,26 +6690,6 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6693,10 +6707,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130107319</v>
+        <v>130107318</v>
       </c>
       <c r="B53" t="n">
-        <v>97794</v>
+        <v>97983</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6732,10 +6746,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>507144</v>
+        <v>507226</v>
       </c>
       <c r="R53" t="n">
-        <v>7033068</v>
+        <v>7033130</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6797,6 +6811,229 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>130107319</v>
+      </c>
+      <c r="B54" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Getsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>507144</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7033068</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>130108128</v>
+      </c>
+      <c r="B55" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Getsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>507058</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7032972</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56557-2025 artfynd.xlsx
+++ b/artfynd/A 56557-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -807,6 +812,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107329</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107332</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107338</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1142,6 +1162,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107339</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1244,6 +1269,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107358</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1346,6 +1376,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107359</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1477,6 +1512,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107360</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1608,6 +1648,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107361</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1710,6 +1755,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107362</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1812,6 +1862,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107363</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1914,6 +1969,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107364</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2016,6 +2076,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107365</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2118,6 +2183,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107366</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2220,6 +2290,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107367</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2322,6 +2397,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107368</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2424,6 +2504,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107369</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2555,6 +2640,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107370</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2657,6 +2747,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107371</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2759,6 +2854,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107372</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2861,6 +2961,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107373</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2963,6 +3068,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107374</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3084,6 +3194,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108129</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3200,6 +3315,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108130</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3316,6 +3436,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108131</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3432,6 +3557,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108114</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3548,6 +3678,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108115</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3664,6 +3799,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108116</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3799,6 +3939,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107324</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3930,6 +4075,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107325</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4051,6 +4201,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108127</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4186,6 +4341,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107309</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4316,6 +4476,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107327</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4447,6 +4612,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107310</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4582,6 +4752,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107302</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4721,6 +4896,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107306</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4860,6 +5040,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107307</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4990,6 +5175,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108117</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5120,6 +5310,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108118</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5250,6 +5445,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108119</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5380,6 +5580,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108120</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5510,6 +5715,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108121</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5640,6 +5850,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108122</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5770,6 +5985,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108123</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5900,6 +6120,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108124</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6035,6 +6260,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108125</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6153,6 +6383,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108126</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6276,6 +6511,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107328</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6383,6 +6623,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107314</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6490,6 +6735,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107315</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6597,6 +6847,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107316</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6704,6 +6959,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107317</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6811,6 +7071,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107318</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6918,6 +7183,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130107319</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7034,8 +7304,69 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130108128</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>